--- a/outputs/forecast_percent_white_by_tract.xlsx
+++ b/outputs/forecast_percent_white_by_tract.xlsx
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>53.49251192428645</v>
+        <v>52.3705233343577</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>52.28958812476885</v>
+        <v>51.11226365393523</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>51.17375083224746</v>
+        <v>50.03846550844942</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>48.28168572298448</v>
+        <v>42.24955164292795</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>42.75502278930725</v>
+        <v>38.40986608939068</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>38.76613575368747</v>
+        <v>35.63898952874379</v>
       </c>
     </row>
     <row r="12">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>36.09340648554791</v>
+        <v>34.61645895641057</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>34.61631783310817</v>
+        <v>33.14273497788558</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>33.14274043887284</v>
+        <v>31.66902738232237</v>
       </c>
     </row>
     <row r="17">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>35.86421485942535</v>
+        <v>35.26292725639473</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>34.49377893135522</v>
+        <v>33.47469735393128</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>34.00266498734103</v>
+        <v>33.2703703516971</v>
       </c>
     </row>
     <row r="22">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>64.66649451378522</v>
+        <v>63.95637053459407</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>63.95637100120961</v>
+        <v>63.24626816407401</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>63.24626817484801</v>
+        <v>62.53616582587597</v>
       </c>
     </row>
     <row r="27">
@@ -711,7 +711,7 @@
         <v>2024</v>
       </c>
       <c r="D27">
-        <v>40.79621791820556</v>
+        <v>40.79621791820554</v>
       </c>
     </row>
     <row r="28">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>40.53296295776792</v>
+        <v>40.27744520426517</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>40.27584635042745</v>
+        <v>40.02486809618414</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>40.025198491069</v>
+        <v>39.7732821727577</v>
       </c>
     </row>
     <row r="32">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>35.30909979718842</v>
+        <v>34.59583588164004</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>34.59341761135429</v>
+        <v>33.84808557143874</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>33.8478708196557</v>
+        <v>33.09969100588834</v>
       </c>
     </row>
     <row r="37">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>58.40154734231157</v>
+        <v>57.21567345676215</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>57.215668076843</v>
+        <v>56.03007563826743</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>56.03007573731895</v>
+        <v>54.84447811692728</v>
       </c>
     </row>
     <row r="42">
@@ -906,7 +906,7 @@
         <v>2024</v>
       </c>
       <c r="D42">
-        <v>73.26803261703343</v>
+        <v>73.26803261703341</v>
       </c>
     </row>
     <row r="43">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>72.26292182951292</v>
+        <v>72.37430266036471</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>71.8841136264294</v>
+        <v>72.13160800778287</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>72.34682260056302</v>
+        <v>72.53455713354147</v>
       </c>
     </row>
     <row r="47">
@@ -971,7 +971,7 @@
         <v>2024</v>
       </c>
       <c r="D47">
-        <v>30.74809968225166</v>
+        <v>30.74809968225165</v>
       </c>
     </row>
     <row r="48">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>29.94476403848657</v>
+        <v>29.14478906746915</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>29.14462664039092</v>
+        <v>28.34768748796473</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>28.34769533834402</v>
+        <v>27.55060945959819</v>
       </c>
     </row>
     <row r="52">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>27.34245840676418</v>
+        <v>25.8337553860999</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>25.84464799052902</v>
+        <v>24.32739398519762</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>24.32348285405487</v>
+        <v>22.80929919086711</v>
       </c>
     </row>
     <row r="57">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>12.30295123322719</v>
+        <v>11.81600637400529</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>11.81373201959293</v>
+        <v>11.33542233567115</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>11.33581468499279</v>
+        <v>10.85601534530194</v>
       </c>
     </row>
     <row r="62">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>6.063028290971854</v>
+        <v>4.954375099992426</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>4.959572027790785</v>
+        <v>3.881608530654329</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>3.882939249701932</v>
+        <v>2.81283411845904</v>
       </c>
     </row>
     <row r="67">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>4.075088282124878</v>
+        <v>3.608385088306204</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>3.619093807424802</v>
+        <v>3.138154513476552</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>3.134938095964738</v>
+        <v>2.658274686111457</v>
       </c>
     </row>
     <row r="72">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>24.22325926024662</v>
+        <v>24.72082655903863</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>24.72182263417119</v>
+        <v>25.22630112207933</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>25.22650282117132</v>
+        <v>25.73238078239601</v>
       </c>
     </row>
     <row r="77">
@@ -1361,7 +1361,7 @@
         <v>2024</v>
       </c>
       <c r="D77">
-        <v>25.07711935903596</v>
+        <v>25.07711935903597</v>
       </c>
     </row>
     <row r="78">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>26.62583995238396</v>
+        <v>28.11441546459769</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>28.12572324279632</v>
+        <v>29.57676923027304</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>29.57464327341376</v>
+        <v>31.03274512537056</v>
       </c>
     </row>
     <row r="82">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>25.44221451683862</v>
+        <v>24.983880694109</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>24.85313736596436</v>
+        <v>24.48507762565429</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>24.53367263917707</v>
+        <v>24.13205959776792</v>
       </c>
     </row>
     <row r="87">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>20.73744170214773</v>
+        <v>20.32406865287277</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>20.23961782899812</v>
+        <v>19.89473806214486</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>19.92478058094663</v>
+        <v>19.55553502782228</v>
       </c>
     </row>
     <row r="92">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>13.08860365142226</v>
+        <v>12.627090811625</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>12.62953251705864</v>
+        <v>12.16081380353379</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>12.1603206456982</v>
+        <v>11.69305732193581</v>
       </c>
     </row>
     <row r="97">
@@ -1621,7 +1621,7 @@
         <v>2024</v>
       </c>
       <c r="D97">
-        <v>44.13040557850935</v>
+        <v>44.13040557850934</v>
       </c>
     </row>
     <row r="98">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>42.76471875886838</v>
+        <v>40.50296725290484</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>40.93603218620897</v>
+        <v>38.6443458605311</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>38.43504709078783</v>
+        <v>36.15782815892754</v>
       </c>
     </row>
     <row r="102">
@@ -1686,7 +1686,7 @@
         <v>2024</v>
       </c>
       <c r="D102">
-        <v>39.9980530281963</v>
+        <v>39.99805302819631</v>
       </c>
     </row>
     <row r="103">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>37.2046732879684</v>
+        <v>34.39267183776914</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>34.39004685549434</v>
+        <v>31.55417373077414</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>31.55380370396384</v>
+        <v>28.71456554334825</v>
       </c>
     </row>
     <row r="107">
@@ -1751,7 +1751,7 @@
         <v>2024</v>
       </c>
       <c r="D107">
-        <v>86.36950546614473</v>
+        <v>86.3695054661447</v>
       </c>
     </row>
     <row r="108">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>85.99651704402038</v>
+        <v>85.62306280022551</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>85.62307570994365</v>
+        <v>85.24918146391458</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>85.24918110613642</v>
+        <v>84.87529905426918</v>
       </c>
     </row>
     <row r="112">
@@ -1816,7 +1816,7 @@
         <v>2024</v>
       </c>
       <c r="D112">
-        <v>42.58026355543129</v>
+        <v>42.58026355543127</v>
       </c>
     </row>
     <row r="113">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>43.30466506457574</v>
+        <v>44.00440680085369</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>44.00137561648595</v>
+        <v>44.67039521116193</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>44.67002261735416</v>
+        <v>45.33526584004686</v>
       </c>
     </row>
     <row r="117">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>76.05898607728851</v>
+        <v>75.76269518017932</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>75.76034299910056</v>
+        <v>75.47735238906324</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>75.47765968501535</v>
+        <v>75.1929314858035</v>
       </c>
     </row>
     <row r="122">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>75.97109924194717</v>
+        <v>74.06095232022</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>74.0632182701345</v>
+        <v>72.14606952721192</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>72.14562435179938</v>
+        <v>70.22985120796625</v>
       </c>
     </row>
     <row r="127">
@@ -2011,7 +2011,7 @@
         <v>2024</v>
       </c>
       <c r="D127">
-        <v>71.02673717467925</v>
+        <v>71.02673717467924</v>
       </c>
     </row>
     <row r="128">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>71.40557667380246</v>
+        <v>71.80903459258855</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>71.80298885320713</v>
+        <v>72.21897371289327</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>72.22045841277119</v>
+        <v>72.63336693283176</v>
       </c>
     </row>
     <row r="132">
@@ -2076,7 +2076,7 @@
         <v>2024</v>
       </c>
       <c r="D132">
-        <v>47.62138929161969</v>
+        <v>47.62138929161968</v>
       </c>
     </row>
     <row r="133">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>45.91313048587065</v>
+        <v>44.12367338732247</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>44.171168781251</v>
+        <v>42.39550417776078</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>42.36772265223033</v>
+        <v>40.58399039160778</v>
       </c>
     </row>
     <row r="137">
@@ -2141,7 +2141,7 @@
         <v>2024</v>
       </c>
       <c r="D137">
-        <v>68.84604771372868</v>
+        <v>68.84604771372867</v>
       </c>
     </row>
     <row r="138">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>71.26463808523296</v>
+        <v>72.49255979192583</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>73.21295670555956</v>
+        <v>74.69100357470852</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>74.25513780574146</v>
+        <v>75.58185005059001</v>
       </c>
     </row>
     <row r="142">
@@ -2206,7 +2206,7 @@
         <v>2024</v>
       </c>
       <c r="D142">
-        <v>38.46008283280806</v>
+        <v>38.46008283280804</v>
       </c>
     </row>
     <row r="143">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>38.5405785453492</v>
+        <v>38.50810090681895</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>38.58117882477068</v>
+        <v>38.5818836710725</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>38.53461250454062</v>
+        <v>38.51385293573042</v>
       </c>
     </row>
     <row r="147">
@@ -2271,7 +2271,7 @@
         <v>2024</v>
       </c>
       <c r="D147">
-        <v>86.45029874990631</v>
+        <v>86.4502987499063</v>
       </c>
     </row>
     <row r="148">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>86.40272625911307</v>
+        <v>86.4195593173885</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>86.45040166883496</v>
+        <v>86.59332497907198</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>86.60809467914443</v>
+        <v>86.81139974097279</v>
       </c>
     </row>
     <row r="152">
@@ -2336,7 +2336,7 @@
         <v>2024</v>
       </c>
       <c r="D152">
-        <v>74.93144086444184</v>
+        <v>74.93144086444183</v>
       </c>
     </row>
     <row r="153">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>73.3692300243966</v>
+        <v>71.80701918472528</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>71.80701918470415</v>
+        <v>70.2448083453645</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>70.2448083453657</v>
+        <v>68.6825975060073</v>
       </c>
     </row>
     <row r="157">
@@ -2401,7 +2401,7 @@
         <v>2024</v>
       </c>
       <c r="D157">
-        <v>74.4236231066333</v>
+        <v>74.42362310663329</v>
       </c>
     </row>
     <row r="158">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>68.52715210155286</v>
+        <v>62.7831104246286</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>62.68261955250279</v>
+        <v>56.89002545948311</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>56.95627527835169</v>
+        <v>51.19568995094335</v>
       </c>
     </row>
     <row r="162">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>74.38778603098636</v>
+        <v>73.47728462645561</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>72.81564483418704</v>
+        <v>71.51265144410797</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>71.98297057512001</v>
+        <v>70.95897565479645</v>
       </c>
     </row>
     <row r="167">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>59.90139243866727</v>
+        <v>59.58049764472598</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>59.69789732116342</v>
+        <v>59.33612335234464</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>59.28612785889802</v>
+        <v>58.94176257962346</v>
       </c>
     </row>
     <row r="172">
@@ -2596,7 +2596,7 @@
         <v>2024</v>
       </c>
       <c r="D172">
-        <v>66.42872270893234</v>
+        <v>66.42872270893236</v>
       </c>
     </row>
     <row r="173">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>66.70439382445328</v>
+        <v>66.99303957815377</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>66.99489694771016</v>
+        <v>67.30023207870302</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>67.30049796832718</v>
+        <v>67.60822224812475</v>
       </c>
     </row>
     <row r="177">
@@ -2661,7 +2661,7 @@
         <v>2024</v>
       </c>
       <c r="D177">
-        <v>67.70724117529086</v>
+        <v>67.70724117529085</v>
       </c>
     </row>
     <row r="178">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>65.58481451001289</v>
+        <v>63.4826398347608</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>63.48538237711739</v>
+        <v>61.40894477660436</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>61.4093161741099</v>
+        <v>59.33636391096455</v>
       </c>
     </row>
     <row r="182">
@@ -2726,7 +2726,7 @@
         <v>2024</v>
       </c>
       <c r="D182">
-        <v>83.25228669360899</v>
+        <v>83.25228669360901</v>
       </c>
     </row>
     <row r="183">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>81.55125912804895</v>
+        <v>80.02992802390301</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>80.13426821168019</v>
+        <v>79.00131394450273</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>79.06189874789676</v>
+        <v>78.15445427528458</v>
       </c>
     </row>
     <row r="187">
@@ -2791,7 +2791,7 @@
         <v>2024</v>
       </c>
       <c r="D187">
-        <v>88.7726614897835</v>
+        <v>88.77266148978352</v>
       </c>
     </row>
     <row r="188">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>88.73757263656232</v>
+        <v>88.73239605781447</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>88.74577707384572</v>
+        <v>88.79727480163369</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>88.80326069181358</v>
+        <v>88.88011121599257</v>
       </c>
     </row>
     <row r="192">
@@ -2856,7 +2856,7 @@
         <v>2024</v>
       </c>
       <c r="D192">
-        <v>51.62561425523962</v>
+        <v>51.6256142552396</v>
       </c>
     </row>
     <row r="193">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>50.70213689144951</v>
+        <v>49.82134049032473</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>49.80883542305136</v>
+        <v>48.94570985004515</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>48.94937370150833</v>
+        <v>48.08107076415514</v>
       </c>
     </row>
     <row r="197">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>27.74618166424208</v>
+        <v>27.40579425402705</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>27.32546873098363</v>
+        <v>26.97031504817212</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>27.01454303371048</v>
+        <v>26.66751979893229</v>
       </c>
     </row>
     <row r="202">
@@ -2986,7 +2986,7 @@
         <v>2024</v>
       </c>
       <c r="D202">
-        <v>21.97271300721498</v>
+        <v>21.97271300721497</v>
       </c>
     </row>
     <row r="203">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>24.87950385497129</v>
+        <v>25.80802808754159</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>27.49073261114177</v>
+        <v>29.80639927572641</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>28.37509851373167</v>
+        <v>29.51086817792701</v>
       </c>
     </row>
     <row r="207">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>32.22216285239864</v>
+        <v>31.1692060709171</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>31.17219294728341</v>
+        <v>30.11322290866427</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>30.11247865046108</v>
+        <v>29.05500697180187</v>
       </c>
     </row>
     <row r="212">
@@ -3116,7 +3116,7 @@
         <v>2024</v>
       </c>
       <c r="D212">
-        <v>64.38010975346086</v>
+        <v>64.38010975346084</v>
       </c>
     </row>
     <row r="213">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>66.6586202296361</v>
+        <v>68.91714221483858</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>68.91910748477343</v>
+        <v>71.16157151887285</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>71.16137829338514</v>
+        <v>73.405421146444</v>
       </c>
     </row>
     <row r="217">
@@ -3181,7 +3181,7 @@
         <v>2024</v>
       </c>
       <c r="D217">
-        <v>61.77695121749778</v>
+        <v>61.77695121749777</v>
       </c>
     </row>
     <row r="218">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>63.09031483047134</v>
+        <v>64.3587936675885</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>64.34726481371007</v>
+        <v>65.54780116721398</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>65.54483992992996</v>
+        <v>66.72792495498742</v>
       </c>
     </row>
     <row r="222">
@@ -3246,7 +3246,7 @@
         <v>2024</v>
       </c>
       <c r="D222">
-        <v>86.94554140915461</v>
+        <v>86.94554140915457</v>
       </c>
     </row>
     <row r="223">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>86.28188718716909</v>
+        <v>85.61244294681811</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>85.61384085930852</v>
+        <v>84.94140242557292</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>84.94106492071411</v>
+        <v>84.26934938975135</v>
       </c>
     </row>
     <row r="227">
@@ -3311,7 +3311,7 @@
         <v>2024</v>
       </c>
       <c r="D227">
-        <v>86.81434423734774</v>
+        <v>86.81434423734771</v>
       </c>
     </row>
     <row r="228">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>85.9901521015189</v>
+        <v>85.08806647668473</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>85.05679582888006</v>
+        <v>84.0142754194312</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>84.00172169476679</v>
+        <v>82.90282318818444</v>
       </c>
     </row>
     <row r="232">
@@ -3376,7 +3376,7 @@
         <v>2024</v>
       </c>
       <c r="D232">
-        <v>69.37156901489926</v>
+        <v>69.37156901489925</v>
       </c>
     </row>
     <row r="233">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>69.35737720663785</v>
+        <v>69.38923543641002</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>69.3818272374878</v>
+        <v>69.4449191074491</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>69.44611088521117</v>
+        <v>69.50417811177441</v>
       </c>
     </row>
     <row r="237">
@@ -3441,7 +3441,7 @@
         <v>2024</v>
       </c>
       <c r="D237">
-        <v>46.77481208154243</v>
+        <v>46.77481208154242</v>
       </c>
     </row>
     <row r="238">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>46.74973021764428</v>
+        <v>46.96539013082036</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>46.85228618204983</v>
+        <v>47.0824799747591</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>47.1356178363424</v>
+        <v>47.35898340344772</v>
       </c>
     </row>
     <row r="242">
@@ -3506,7 +3506,7 @@
         <v>2024</v>
       </c>
       <c r="D242">
-        <v>80.72605825839024</v>
+        <v>80.72605825839021</v>
       </c>
     </row>
     <row r="243">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>81.02773980939423</v>
+        <v>81.32603517117175</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>81.32648228789323</v>
+        <v>81.62228569388721</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>81.62222665602806</v>
+        <v>81.91835910302522</v>
       </c>
     </row>
     <row r="247">
@@ -3571,7 +3571,7 @@
         <v>2024</v>
       </c>
       <c r="D247">
-        <v>92.45840734973963</v>
+        <v>92.45840734973962</v>
       </c>
     </row>
     <row r="248">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>92.4028660041335</v>
+        <v>92.33930754821704</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>92.33563712968304</v>
+        <v>92.25672072638821</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>92.25504032388739</v>
+        <v>92.16909269705691</v>
       </c>
     </row>
     <row r="252">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>81.21628213070898</v>
+        <v>81.36203590660382</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>81.35910801338623</v>
+        <v>81.51378828201992</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>81.51436820332925</v>
+        <v>81.66728042136401</v>
       </c>
     </row>
     <row r="257">
@@ -3701,7 +3701,7 @@
         <v>2024</v>
       </c>
       <c r="D257">
-        <v>44.49419390265793</v>
+        <v>44.49419390265792</v>
       </c>
     </row>
     <row r="258">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>45.3642342792453</v>
+        <v>46.09384079160698</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>46.15407190774535</v>
+        <v>46.86370678815805</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>46.83787407771263</v>
+        <v>47.55607465337287</v>
       </c>
     </row>
     <row r="262">
@@ -3766,7 +3766,7 @@
         <v>2024</v>
       </c>
       <c r="D262">
-        <v>51.60650924733244</v>
+        <v>51.60650924733243</v>
       </c>
     </row>
     <row r="263">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>52.4529249360159</v>
+        <v>53.28745570969227</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>53.28545000378523</v>
+        <v>54.1040844506404</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>54.10374596642043</v>
+        <v>54.91969773892864</v>
       </c>
     </row>
     <row r="267">
@@ -3831,7 +3831,7 @@
         <v>2024</v>
       </c>
       <c r="D267">
-        <v>70.4620100566836</v>
+        <v>70.46201005668357</v>
       </c>
     </row>
     <row r="268">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>71.45350629091091</v>
+        <v>72.47043301764924</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>72.47302544401222</v>
+        <v>73.52056751598755</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>73.5208317922081</v>
+        <v>74.57149484298751</v>
       </c>
     </row>
     <row r="272">
@@ -3896,7 +3896,7 @@
         <v>2024</v>
       </c>
       <c r="D272">
-        <v>78.72112351103726</v>
+        <v>78.72112351103723</v>
       </c>
     </row>
     <row r="273">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>78.56710290010348</v>
+        <v>78.41310859799118</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>78.41310892765721</v>
+        <v>78.25914159369844</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>78.25914159782936</v>
+        <v>78.10517460179847</v>
       </c>
     </row>
     <row r="277">
@@ -3961,7 +3961,7 @@
         <v>2024</v>
       </c>
       <c r="D277">
-        <v>59.88585051604833</v>
+        <v>59.88585051604831</v>
       </c>
     </row>
     <row r="278">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>61.19016889846981</v>
+        <v>62.58093384772181</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>62.62385950410893</v>
+        <v>64.18692233296569</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>64.20823737234578</v>
+        <v>65.85685593634983</v>
       </c>
     </row>
     <row r="282">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>33.2956749555025</v>
+        <v>33.89323155712957</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>33.89488082158667</v>
+        <v>34.47708800294576</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>34.4769421384744</v>
+        <v>35.06050685534787</v>
       </c>
     </row>
     <row r="287">
@@ -4091,7 +4091,7 @@
         <v>2024</v>
       </c>
       <c r="D287">
-        <v>10.67170633105352</v>
+        <v>10.67170633105353</v>
       </c>
     </row>
     <row r="288">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>11.10973825641945</v>
+        <v>11.54775266762781</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>11.54775565752453</v>
+        <v>11.98575853436878</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>11.98575802395414</v>
+        <v>12.42376286986584</v>
       </c>
     </row>
     <row r="292">
@@ -4156,7 +4156,7 @@
         <v>2024</v>
       </c>
       <c r="D292">
-        <v>6.130715847360239</v>
+        <v>6.130715847360241</v>
       </c>
     </row>
     <row r="293">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>7.310720824775746</v>
+        <v>8.068701763075945</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>8.421854433136431</v>
+        <v>9.464116672442294</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>9.168596046100022</v>
+        <v>9.972969702781834</v>
       </c>
     </row>
     <row r="297">
@@ -4221,7 +4221,7 @@
         <v>2024</v>
       </c>
       <c r="D297">
-        <v>30.52818182218853</v>
+        <v>30.52818182218852</v>
       </c>
     </row>
     <row r="298">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>32.14317006444652</v>
+        <v>33.53867567176586</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>33.63791843285087</v>
+        <v>35.01242692740161</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>34.96755264552264</v>
+        <v>36.35155533740044</v>
       </c>
     </row>
     <row r="302">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>35.37009777197563</v>
+        <v>36.98920151357314</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>36.9451464014827</v>
+        <v>38.40342262160704</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>38.37673223330095</v>
+        <v>39.73757256472267</v>
       </c>
     </row>
     <row r="307">
@@ -4351,7 +4351,7 @@
         <v>2024</v>
       </c>
       <c r="D307">
-        <v>63.20987176533744</v>
+        <v>63.20987176533743</v>
       </c>
     </row>
     <row r="308">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>61.5888911765939</v>
+        <v>59.94623776932538</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>59.94917299467096</v>
+        <v>58.29071721956865</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>58.29031969177043</v>
+        <v>56.63400408641728</v>
       </c>
     </row>
     <row r="312">
@@ -4416,7 +4416,7 @@
         <v>2024</v>
       </c>
       <c r="D312">
-        <v>63.18699848193233</v>
+        <v>63.18699848193234</v>
       </c>
     </row>
     <row r="313">
@@ -4442,7 +4442,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>61.56564887241158</v>
+        <v>60.13998406849012</v>
       </c>
     </row>
     <row r="315">
@@ -4455,7 +4455,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>60.2132153408722</v>
+        <v>59.12969788731418</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4468,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>59.1571032816077</v>
+        <v>58.20162788901882</v>
       </c>
     </row>
     <row r="317">
@@ -4481,7 +4481,7 @@
         <v>2024</v>
       </c>
       <c r="D317">
-        <v>33.13062302251795</v>
+        <v>33.13062302251794</v>
       </c>
     </row>
     <row r="318">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>29.3850564118084</v>
+        <v>26.04213506120005</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>25.86475974479262</v>
+        <v>22.56973302147061</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>22.64787128854651</v>
+        <v>19.3317457829689</v>
       </c>
     </row>
     <row r="322">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>83.267826292386</v>
+        <v>82.96000803294267</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>82.96416357020934</v>
+        <v>82.64369973585356</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>82.6428757257932</v>
+        <v>82.3249194085834</v>
       </c>
     </row>
     <row r="327">
@@ -4611,7 +4611,7 @@
         <v>2024</v>
       </c>
       <c r="D327">
-        <v>92.28377782539191</v>
+        <v>92.28377782539189</v>
       </c>
     </row>
     <row r="328">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>92.19367978304403</v>
+        <v>92.80817703801621</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>92.34215816463556</v>
+        <v>92.72921297016647</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>93.03743755124587</v>
+        <v>93.57492264555489</v>
       </c>
     </row>
     <row r="332">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>64.45876900370563</v>
+        <v>60.70516258960811</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>60.9262409613707</v>
+        <v>57.92667512547846</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>58.08338618590047</v>
+        <v>55.61832084261484</v>
       </c>
     </row>
     <row r="337">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>19.74488023173672</v>
+        <v>19.22295823922068</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>19.22329553689244</v>
+        <v>18.70295536062925</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>18.70308076527789</v>
+        <v>18.18332869598375</v>
       </c>
     </row>
     <row r="342">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>89.88230810751264</v>
+        <v>90.22384552866235</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>90.21900143882952</v>
+        <v>90.56914606943072</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>90.57042864430018</v>
+        <v>90.91829433480748</v>
       </c>
     </row>
     <row r="347">
@@ -4871,7 +4871,7 @@
         <v>2024</v>
       </c>
       <c r="D347">
-        <v>55.9605332991474</v>
+        <v>55.96053329914739</v>
       </c>
     </row>
     <row r="348">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>55.02256106495582</v>
+        <v>54.0906588439852</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>54.09025764047743</v>
+        <v>53.16362302571223</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>53.16364954365358</v>
+        <v>52.23666676126333</v>
       </c>
     </row>
     <row r="352">
@@ -4936,7 +4936,7 @@
         <v>2024</v>
       </c>
       <c r="D352">
-        <v>51.9976137361904</v>
+        <v>51.99761373619041</v>
       </c>
     </row>
     <row r="353">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>49.29066497602013</v>
+        <v>46.54374836590051</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>46.55329144044345</v>
+        <v>43.78549312946038</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>43.78321454124892</v>
+        <v>41.02040212838585</v>
       </c>
     </row>
     <row r="357">
@@ -5027,7 +5027,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>66.91311789435042</v>
+        <v>65.4027450005584</v>
       </c>
     </row>
     <row r="360">
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>65.76340515799762</v>
+        <v>64.27666970374133</v>
       </c>
     </row>
     <row r="361">
@@ -5053,7 +5053,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>64.09023005650162</v>
+        <v>62.59127546520514</v>
       </c>
     </row>
     <row r="362">
@@ -5066,7 +5066,7 @@
         <v>2024</v>
       </c>
       <c r="D362">
-        <v>42.87191677150696</v>
+        <v>42.87191677150697</v>
       </c>
     </row>
     <row r="363">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>39.98423148838525</v>
+        <v>37.09421188801481</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>37.09508951827883</v>
+        <v>34.20449086118772</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>34.20416089966225</v>
+        <v>31.31377994978422</v>
       </c>
     </row>
     <row r="367">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>14.19465641259931</v>
+        <v>11.8958652610804</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>11.85679426166522</v>
+        <v>9.544983760603596</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>9.568424806261278</v>
+        <v>7.264425397099843</v>
       </c>
     </row>
     <row r="372">
@@ -5196,7 +5196,7 @@
         <v>2024</v>
       </c>
       <c r="D372">
-        <v>30.2378488467976</v>
+        <v>30.23784884679759</v>
       </c>
     </row>
     <row r="373">
@@ -5222,7 +5222,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>26.57295228068479</v>
+        <v>22.64107053248182</v>
       </c>
     </row>
     <row r="375">
@@ -5235,7 +5235,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>22.86491568043953</v>
+        <v>19.1137390460618</v>
       </c>
     </row>
     <row r="376">
@@ -5248,7 +5248,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>18.92606327367648</v>
+        <v>15.02338024248583</v>
       </c>
     </row>
     <row r="377">
@@ -5261,7 +5261,7 @@
         <v>2024</v>
       </c>
       <c r="D377">
-        <v>82.22484120416944</v>
+        <v>82.22484120416942</v>
       </c>
     </row>
     <row r="378">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>84.17439733038638</v>
+        <v>86.16464114714606</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>86.15743020522264</v>
+        <v>88.17393982867819</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>88.17521779955166</v>
+        <v>90.18707242283079</v>
       </c>
     </row>
     <row r="382">
@@ -5326,7 +5326,7 @@
         <v>2024</v>
       </c>
       <c r="D382">
-        <v>70.71877899704735</v>
+        <v>70.71877899704737</v>
       </c>
     </row>
     <row r="383">
@@ -5352,7 +5352,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>70.13362526322719</v>
+        <v>69.7547225365183</v>
       </c>
     </row>
     <row r="385">
@@ -5365,7 +5365,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>69.66199813021854</v>
+        <v>69.30389759802141</v>
       </c>
     </row>
     <row r="386">
@@ -5378,7 +5378,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>69.34558377276579</v>
+        <v>68.97813118375765</v>
       </c>
     </row>
     <row r="387">
@@ -5417,7 +5417,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>47.25165460476632</v>
+        <v>49.47894041070111</v>
       </c>
     </row>
     <row r="390">
@@ -5430,7 +5430,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>49.47893833498318</v>
+        <v>51.70611791873134</v>
       </c>
     </row>
     <row r="391">
@@ -5443,7 +5443,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>51.70611787651941</v>
+        <v>53.93329530012576</v>
       </c>
     </row>
     <row r="392">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>34.24656556235263</v>
+        <v>32.20513739666816</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>31.9475326361915</v>
+        <v>29.85822390653183</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>30.00022283818234</v>
+        <v>27.93730721134702</v>
       </c>
     </row>
     <row r="397">
@@ -5547,7 +5547,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>45.22654696040509</v>
+        <v>44.32090081426387</v>
       </c>
     </row>
     <row r="400">
@@ -5560,7 +5560,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>44.3209008140794</v>
+        <v>43.4152546693181</v>
       </c>
     </row>
     <row r="401">
@@ -5573,7 +5573,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>43.41525466933755</v>
+        <v>42.50960852443072</v>
       </c>
     </row>
     <row r="402">
@@ -5612,7 +5612,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>12.57337150421291</v>
+        <v>6.806167074949727</v>
       </c>
     </row>
     <row r="405">
@@ -5625,7 +5625,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>6.806167081208109</v>
+        <v>1.038958124462766</v>
       </c>
     </row>
     <row r="406">
@@ -5638,7 +5638,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>1.038958124454136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>44.15480452957974</v>
+        <v>44.1003388111142</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>44.1029238212574</v>
+        <v>44.0342442491615</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>44.03389951531371</v>
+        <v>43.96711548566543</v>
       </c>
     </row>
     <row r="412">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>39.32294540037756</v>
+        <v>42.1940400955911</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>42.20109226731683</v>
+        <v>45.11405091396202</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>45.11584247838486</v>
+        <v>48.03943642560147</v>
       </c>
     </row>
     <row r="417">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>13.66622861272803</v>
+        <v>11.35941302809364</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>11.50131706348042</v>
+        <v>9.662482588343602</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>9.77181865294113</v>
+        <v>8.293560342386147</v>
       </c>
     </row>
     <row r="422">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>18.1389560205157</v>
+        <v>18.42648318161946</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>18.41409804664987</v>
+        <v>18.63376683668663</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>18.63020688476951</v>
+        <v>18.83037063600245</v>
       </c>
     </row>
     <row r="427">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>11.29008777332051</v>
+        <v>11.2433055048103</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>10.96350869228332</v>
+        <v>10.81226534046174</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>10.98427294071049</v>
+        <v>10.89724797685943</v>
       </c>
     </row>
     <row r="432">
@@ -5976,7 +5976,7 @@
         <v>2024</v>
       </c>
       <c r="D432">
-        <v>4.045076998523268</v>
+        <v>4.045076998523267</v>
       </c>
     </row>
     <row r="433">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>3.974657073465047</v>
+        <v>3.897538959274752</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>3.89882792228412</v>
+        <v>3.817589544980486</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>3.817341503964212</v>
+        <v>3.736896007637398</v>
       </c>
     </row>
     <row r="437">
@@ -6041,7 +6041,7 @@
         <v>2024</v>
       </c>
       <c r="D437">
-        <v>66.04283672927532</v>
+        <v>66.04283672927531</v>
       </c>
     </row>
     <row r="438">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>63.74968146091544</v>
+        <v>61.43080488742225</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>61.4436619034127</v>
+        <v>59.1247780567671</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>59.11835136654583</v>
+        <v>56.79947115544814</v>
       </c>
     </row>
     <row r="442">
@@ -6106,7 +6106,7 @@
         <v>2024</v>
       </c>
       <c r="D442">
-        <v>37.42030803107486</v>
+        <v>37.42030803107487</v>
       </c>
     </row>
     <row r="443">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>37.08001258836631</v>
+        <v>36.74904050478808</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>36.74956762635281</v>
+        <v>36.42897314503436</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>36.42900294729127</v>
+        <v>36.10899519205137</v>
       </c>
     </row>
     <row r="447">
@@ -6171,7 +6171,7 @@
         <v>2024</v>
       </c>
       <c r="D447">
-        <v>26.29360397441864</v>
+        <v>26.29360397441865</v>
       </c>
     </row>
     <row r="448">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>25.41306884113438</v>
+        <v>24.52427128631483</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>24.52812802250923</v>
+        <v>23.63878151854319</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>23.63698126978927</v>
+        <v>22.74789100450982</v>
       </c>
     </row>
     <row r="452">
@@ -6262,7 +6262,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>38.53497806430409</v>
+        <v>36.48947048766464</v>
       </c>
     </row>
     <row r="455">
@@ -6275,7 +6275,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>36.48798536231568</v>
+        <v>34.44523282877138</v>
       </c>
     </row>
     <row r="456">
@@ -6288,7 +6288,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>34.44561806617261</v>
+        <v>32.40215088208181</v>
       </c>
     </row>
     <row r="457">
@@ -6301,7 +6301,7 @@
         <v>2024</v>
       </c>
       <c r="D457">
-        <v>47.31267380409852</v>
+        <v>47.31267380409851</v>
       </c>
     </row>
     <row r="458">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>45.49979875867845</v>
+        <v>43.62596868768426</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>43.58931149834046</v>
+        <v>41.58121202308454</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>41.55916708884112</v>
+        <v>39.47032055575457</v>
       </c>
     </row>
     <row r="462">
@@ -6366,7 +6366,7 @@
         <v>2024</v>
       </c>
       <c r="D462">
-        <v>53.35603887763975</v>
+        <v>53.35603887763976</v>
       </c>
     </row>
     <row r="463">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>50.60250647186933</v>
+        <v>47.48445206889097</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>47.68522742359733</v>
+        <v>44.60420173282376</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>44.49361651885526</v>
+        <v>41.39219575485104</v>
       </c>
     </row>
     <row r="467">
@@ -6431,7 +6431,7 @@
         <v>2024</v>
       </c>
       <c r="D467">
-        <v>54.43385120157122</v>
+        <v>54.4338512015712</v>
       </c>
     </row>
     <row r="468">
@@ -6457,7 +6457,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>51.72008973862294</v>
+        <v>49.0058182489434</v>
       </c>
     </row>
     <row r="470">
@@ -6470,7 +6470,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>49.00579758440517</v>
+        <v>46.2909747389179</v>
       </c>
     </row>
     <row r="471">
@@ -6483,7 +6483,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>46.29097390166152</v>
+        <v>43.57612871712325</v>
       </c>
     </row>
     <row r="472">
@@ -6496,7 +6496,7 @@
         <v>2024</v>
       </c>
       <c r="D472">
-        <v>40.91632946089708</v>
+        <v>40.91632946089707</v>
       </c>
     </row>
     <row r="473">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>43.81436592417528</v>
+        <v>47.3650957073719</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>46.83072869402478</v>
+        <v>49.96541777044559</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>50.40290976896828</v>
+        <v>53.87821582908735</v>
       </c>
     </row>
     <row r="477">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>13.75899573903533</v>
+        <v>11.47415582749074</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>11.48726658851741</v>
+        <v>9.274893588617346</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>9.2786105441067</v>
+        <v>7.086782216212024</v>
       </c>
     </row>
     <row r="482">
@@ -6626,7 +6626,7 @@
         <v>2024</v>
       </c>
       <c r="D482">
-        <v>42.17880590874247</v>
+        <v>42.17880590874246</v>
       </c>
     </row>
     <row r="483">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>41.78621048577441</v>
+        <v>41.36489940149085</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>41.36976880611864</v>
+        <v>40.92948086977515</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>40.92865514958126</v>
+        <v>40.49158517747779</v>
       </c>
     </row>
     <row r="487">
@@ -6691,7 +6691,7 @@
         <v>2024</v>
       </c>
       <c r="D487">
-        <v>5.77626380440563</v>
+        <v>5.776263804405629</v>
       </c>
     </row>
     <row r="488">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>4.469133960009903</v>
+        <v>3.161397506876131</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>3.16121710734923</v>
+        <v>1.852513246423612</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>1.852459597362422</v>
+        <v>0.5434680387875235</v>
       </c>
     </row>
     <row r="492">
@@ -6756,7 +6756,7 @@
         <v>2024</v>
       </c>
       <c r="D492">
-        <v>24.66723369562022</v>
+        <v>24.66723369562021</v>
       </c>
     </row>
     <row r="493">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>25.51532704405285</v>
+        <v>26.36341943027825</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>26.36341943127935</v>
+        <v>27.21151085729972</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>27.21151085729868</v>
+        <v>28.05960228431807</v>
       </c>
     </row>
     <row r="497">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>18.68121105076855</v>
+        <v>17.41567144077293</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>17.41586272155743</v>
+        <v>16.15122733527135</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>16.15129747327002</v>
+        <v>14.88699364376577</v>
       </c>
     </row>
     <row r="502">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>43.95242002973178</v>
+        <v>47.01108926235673</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>46.81598220641812</v>
+        <v>49.13026695126673</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>49.02278545121074</v>
+        <v>50.92700014000874</v>
       </c>
     </row>
     <row r="507">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>34.82712756393021</v>
+        <v>36.21816595533522</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>36.21801587680346</v>
+        <v>37.60563037073784</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>37.60562316029051</v>
+        <v>38.99307315479847</v>
       </c>
     </row>
     <row r="512">
@@ -7016,7 +7016,7 @@
         <v>2024</v>
       </c>
       <c r="D512">
-        <v>74.89959158346832</v>
+        <v>74.89959158346834</v>
       </c>
     </row>
     <row r="513">
@@ -7042,7 +7042,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>73.39361837538242</v>
+        <v>71.88765385893059</v>
       </c>
     </row>
     <row r="515">
@@ -7055,7 +7055,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>71.88765383779669</v>
+        <v>70.38169797071112</v>
       </c>
     </row>
     <row r="516">
@@ -7068,7 +7068,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>70.3816979707625</v>
+        <v>68.87574208264581</v>
       </c>
     </row>
     <row r="517">
@@ -7081,7 +7081,7 @@
         <v>2024</v>
       </c>
       <c r="D517">
-        <v>42.34726451664558</v>
+        <v>42.34726451664557</v>
       </c>
     </row>
     <row r="518">
@@ -7107,7 +7107,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>39.74187174100708</v>
+        <v>37.29870579999678</v>
       </c>
     </row>
     <row r="520">
@@ -7120,7 +7120,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>37.21829897605363</v>
+        <v>34.77654622178523</v>
       </c>
     </row>
     <row r="521">
@@ -7133,7 +7133,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>34.81639941470146</v>
+        <v>32.37394622232235</v>
       </c>
     </row>
     <row r="522">
@@ -7146,7 +7146,7 @@
         <v>2024</v>
       </c>
       <c r="D522">
-        <v>51.03384594561788</v>
+        <v>51.03384594561786</v>
       </c>
     </row>
     <row r="523">
@@ -7172,7 +7172,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>53.37051014498682</v>
+        <v>53.51097389960253</v>
       </c>
     </row>
     <row r="525">
@@ -7185,7 +7185,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>55.67441148639156</v>
+        <v>57.94554996983209</v>
       </c>
     </row>
     <row r="526">
@@ -7198,7 +7198,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>55.81438648559128</v>
+        <v>55.98663558733922</v>
       </c>
     </row>
     <row r="527">
@@ -7237,7 +7237,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>44.8655504983951</v>
+        <v>42.04221105524145</v>
       </c>
     </row>
     <row r="530">
@@ -7250,7 +7250,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>41.76575084681488</v>
+        <v>38.83998704288149</v>
       </c>
     </row>
     <row r="531">
@@ -7263,7 +7263,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>39.00964501393997</v>
+        <v>36.14673694369698</v>
       </c>
     </row>
     <row r="532">
@@ -7276,7 +7276,7 @@
         <v>2024</v>
       </c>
       <c r="D532">
-        <v>93.17803008499811</v>
+        <v>93.1780300849981</v>
       </c>
     </row>
     <row r="533">
@@ -7302,7 +7302,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>92.64872010062038</v>
+        <v>92.09716080511527</v>
       </c>
     </row>
     <row r="535">
@@ -7315,7 +7315,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>92.08645250022613</v>
+        <v>91.49122728381538</v>
       </c>
     </row>
     <row r="536">
@@ -7328,7 +7328,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>91.48607351555073</v>
+        <v>90.8698324577215</v>
       </c>
     </row>
     <row r="537">
@@ -7341,7 +7341,7 @@
         <v>2024</v>
       </c>
       <c r="D537">
-        <v>38.70540900735221</v>
+        <v>38.7054090073522</v>
       </c>
     </row>
     <row r="538">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>37.65974088177125</v>
+        <v>36.60794150118489</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>36.60875186564858</v>
+        <v>35.55244195898418</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>35.55233485357699</v>
+        <v>34.49662110056189</v>
       </c>
     </row>
     <row r="542">
@@ -7406,7 +7406,7 @@
         <v>2024</v>
       </c>
       <c r="D542">
-        <v>7.169925739057855</v>
+        <v>7.169925739057853</v>
       </c>
     </row>
     <row r="543">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>6.632854384336582</v>
+        <v>6.095355115978535</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>6.095266887833724</v>
+        <v>5.557163249549284</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>5.557145058482519</v>
+        <v>5.018916809919733</v>
       </c>
     </row>
     <row r="547">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>17.31384334762282</v>
+        <v>17.57385548582716</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>17.56872887521052</v>
+        <v>17.84159794839949</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>17.84273520321364</v>
+        <v>18.11275217541428</v>
       </c>
     </row>
     <row r="552">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>43.72875590287879</v>
+        <v>42.35159493434496</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>42.35012499849976</v>
+        <v>40.97343349514145</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>40.97406725809125</v>
+        <v>39.59717334478735</v>
       </c>
     </row>
     <row r="557">
@@ -7601,7 +7601,7 @@
         <v>2024</v>
       </c>
       <c r="D557">
-        <v>41.2569001708136</v>
+        <v>41.25690017081359</v>
       </c>
     </row>
     <row r="558">
@@ -7627,7 +7627,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>38.19645240927938</v>
+        <v>40.28814259496967</v>
       </c>
     </row>
     <row r="560">
@@ -7640,7 +7640,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>35.26606871534471</v>
+        <v>32.4657490890096</v>
       </c>
     </row>
     <row r="561">
@@ -7653,7 +7653,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>37.36104232664469</v>
+        <v>39.32923529595482</v>
       </c>
     </row>
     <row r="562">
@@ -7692,7 +7692,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>55.3281227185679</v>
+        <v>50.71374768319681</v>
       </c>
     </row>
     <row r="565">
@@ -7705,7 +7705,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>50.4472587894706</v>
+        <v>45.7402344247672</v>
       </c>
     </row>
     <row r="566">
@@ -7718,7 +7718,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>45.90151478076012</v>
+        <v>41.25056223431635</v>
       </c>
     </row>
     <row r="567">
@@ -7757,7 +7757,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>48.9542120452601</v>
+        <v>45.76393433048472</v>
       </c>
     </row>
     <row r="570">
@@ -7770,7 +7770,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>45.70751844744484</v>
+        <v>42.50547702416195</v>
       </c>
     </row>
     <row r="571">
@@ -7783,7 +7783,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>42.5369681988775</v>
+        <v>39.34149324198584</v>
       </c>
     </row>
     <row r="572">
@@ -7796,7 +7796,7 @@
         <v>2024</v>
       </c>
       <c r="D572">
-        <v>23.14058106504667</v>
+        <v>23.14058106504666</v>
       </c>
     </row>
     <row r="573">
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>21.59698239525879</v>
+        <v>20.02878181473072</v>
       </c>
     </row>
     <row r="575">
@@ -7835,7 +7835,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>20.0196169247271</v>
+        <v>18.4084846534516</v>
       </c>
     </row>
     <row r="576">
@@ -7848,7 +7848,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>18.40507047925736</v>
+        <v>16.77794496958975</v>
       </c>
     </row>
     <row r="577">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>28.4591742295138</v>
+        <v>29.03611133948439</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>28.9076400697606</v>
+        <v>29.49001712723248</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>29.55292097167869</v>
+        <v>30.13263444831921</v>
       </c>
     </row>
     <row r="582">
@@ -7926,7 +7926,7 @@
         <v>2024</v>
       </c>
       <c r="D582">
-        <v>43.82495331023035</v>
+        <v>43.82495331023034</v>
       </c>
     </row>
     <row r="583">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>43.29168266100144</v>
+        <v>42.93567470550492</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>42.87630328323826</v>
+        <v>42.57881517694081</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>42.59870072481184</v>
+        <v>42.28161229198984</v>
       </c>
     </row>
     <row r="587">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>31.92948797010943</v>
+        <v>28.69353044836784</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>28.68528133062037</v>
+        <v>25.49159003553015</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>25.49274801334747</v>
+        <v>22.29312355614441</v>
       </c>
     </row>
     <row r="592">
@@ -8056,7 +8056,7 @@
         <v>2024</v>
       </c>
       <c r="D592">
-        <v>61.2850975942659</v>
+        <v>61.28509759426589</v>
       </c>
     </row>
     <row r="593">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>59.81401199962915</v>
+        <v>58.43915047623616</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>58.42011721362175</v>
+        <v>57.1034132362437</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>57.1071780435426</v>
+        <v>55.77897041814796</v>
       </c>
     </row>
     <row r="597">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>64.62791800648459</v>
+        <v>61.99033377598226</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>61.99083604152234</v>
+        <v>59.34880706736304</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>59.34876077300555</v>
+        <v>56.70714147567134</v>
       </c>
     </row>
     <row r="602">
@@ -8186,7 +8186,7 @@
         <v>2024</v>
       </c>
       <c r="D602">
-        <v>58.25383227451253</v>
+        <v>58.25383227451255</v>
       </c>
     </row>
     <row r="603">
@@ -8212,7 +8212,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>56.13617947553783</v>
+        <v>54.47423439296986</v>
       </c>
     </row>
     <row r="605">
@@ -8225,7 +8225,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>54.2963830696992</v>
+        <v>52.73444305699664</v>
       </c>
     </row>
     <row r="606">
@@ -8238,7 +8238,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>52.80385397994203</v>
+        <v>51.20288448985958</v>
       </c>
     </row>
     <row r="607">
@@ -8251,7 +8251,7 @@
         <v>2024</v>
       </c>
       <c r="D607">
-        <v>58.58448240503747</v>
+        <v>58.58448240503746</v>
       </c>
     </row>
     <row r="608">
@@ -8277,7 +8277,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>59.58316913706019</v>
+        <v>60.5818583260091</v>
       </c>
     </row>
     <row r="610">
@@ -8290,7 +8290,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>60.5818583170612</v>
+        <v>61.58054994504053</v>
       </c>
     </row>
     <row r="611">
@@ -8303,7 +8303,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>61.58054994507313</v>
+        <v>62.57924156416973</v>
       </c>
     </row>
     <row r="612">
@@ -8316,7 +8316,7 @@
         <v>2024</v>
       </c>
       <c r="D612">
-        <v>28.52473001903952</v>
+        <v>28.52473001903951</v>
       </c>
     </row>
     <row r="613">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>30.66810508179395</v>
+        <v>32.61186594719067</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>32.51071221913548</v>
+        <v>34.05255143106412</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>34.00129216777069</v>
+        <v>35.3394591250573</v>
       </c>
     </row>
     <row r="617">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>24.14733968157837</v>
+        <v>24.4428027479211</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>24.46007847051492</v>
+        <v>24.75635012500331</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>24.74750527257225</v>
+        <v>25.04336294479236</v>
       </c>
     </row>
     <row r="622">
@@ -8446,7 +8446,7 @@
         <v>2024</v>
       </c>
       <c r="D622">
-        <v>48.78563537381311</v>
+        <v>48.78563537381309</v>
       </c>
     </row>
     <row r="623">
@@ -8472,7 +8472,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>51.4196628705249</v>
+        <v>54.02241895148735</v>
       </c>
     </row>
     <row r="625">
@@ -8485,7 +8485,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>54.02977803301204</v>
+        <v>56.61598086127456</v>
       </c>
     </row>
     <row r="626">
@@ -8498,7 +8498,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>56.61424905350094</v>
+        <v>59.20434734774088</v>
       </c>
     </row>
     <row r="627">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>18.53374084910454</v>
+        <v>19.97473441898069</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>20.94796197096145</v>
+        <v>23.18246217671699</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>22.36094075216448</v>
+        <v>23.92562566079578</v>
       </c>
     </row>
     <row r="632">
@@ -8576,7 +8576,7 @@
         <v>2024</v>
       </c>
       <c r="D632">
-        <v>4.24333228229253</v>
+        <v>4.243332282292529</v>
       </c>
     </row>
     <row r="633">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>4.071331043954508</v>
+        <v>3.900826060731336</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>3.900404963134646</v>
+        <v>3.730554039832942</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>3.730672551164452</v>
+        <v>3.560637552929078</v>
       </c>
     </row>
     <row r="637">
@@ -8641,7 +8641,7 @@
         <v>2024</v>
       </c>
       <c r="D637">
-        <v>9.0517417226696</v>
+        <v>9.051741722669599</v>
       </c>
     </row>
     <row r="638">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>9.88243674481196</v>
+        <v>10.72001297936466</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>10.71641500702335</v>
+        <v>11.55367650930378</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>11.55555777734157</v>
+        <v>12.39298384335627</v>
       </c>
     </row>
     <row r="642">
@@ -8706,7 +8706,7 @@
         <v>2024</v>
       </c>
       <c r="D642">
-        <v>9.653880991081374</v>
+        <v>9.653880991081373</v>
       </c>
     </row>
     <row r="643">
@@ -8732,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>10.26099899993466</v>
+        <v>10.87774170456484</v>
       </c>
     </row>
     <row r="645">
@@ -8745,7 +8745,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>10.87951841489443</v>
+        <v>11.50943923596068</v>
       </c>
     </row>
     <row r="646">
@@ -8758,7 +8758,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>11.50976721511643</v>
+        <v>12.14212070482379</v>
       </c>
     </row>
     <row r="647">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>51.54948836205929</v>
+        <v>54.77687356141507</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>54.66199475131549</v>
+        <v>57.86487839173246</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>57.92917437855428</v>
+        <v>61.14577118251532</v>
       </c>
     </row>
     <row r="652">
@@ -8836,7 +8836,7 @@
         <v>2024</v>
       </c>
       <c r="D652">
-        <v>49.51643469352803</v>
+        <v>49.51643469352802</v>
       </c>
     </row>
     <row r="653">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>51.48614725381044</v>
+        <v>53.54566637602858</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>53.56796237093567</v>
+        <v>55.7618800449037</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>55.76741540198876</v>
+        <v>57.99469978503403</v>
       </c>
     </row>
     <row r="657">
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>12.16415207901996</v>
+        <v>13.21616580527072</v>
       </c>
     </row>
     <row r="660">
@@ -8940,7 +8940,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>13.16527354366571</v>
+        <v>14.05315816931942</v>
       </c>
     </row>
     <row r="661">
@@ -8953,7 +8953,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>14.01161450345743</v>
+        <v>14.76551953578216</v>
       </c>
     </row>
     <row r="662">
@@ -8992,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>52.22195609467013</v>
+        <v>55.10293163364992</v>
       </c>
     </row>
     <row r="665">
@@ -9005,7 +9005,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>55.12634324251962</v>
+        <v>57.96209685613134</v>
       </c>
     </row>
     <row r="666">
@@ -9018,7 +9018,7 @@
         <v>2028</v>
       </c>
       <c r="D666">
-        <v>57.95614213205396</v>
+        <v>60.80339790638061</v>
       </c>
     </row>
     <row r="667">
@@ -9031,7 +9031,7 @@
         <v>2024</v>
       </c>
       <c r="D667">
-        <v>80.41328977456283</v>
+        <v>80.41328977456281</v>
       </c>
     </row>
     <row r="668">
@@ -9057,7 +9057,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>82.98486752145044</v>
+        <v>85.48330782312357</v>
       </c>
     </row>
     <row r="670">
@@ -9070,7 +9070,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>85.49814966608203</v>
+        <v>87.95313620845761</v>
       </c>
     </row>
     <row r="671">
@@ -9083,7 +9083,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>87.95012434084646</v>
+        <v>90.41392899095823</v>
       </c>
     </row>
     <row r="672">
@@ -9122,7 +9122,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>50.98554175670449</v>
+        <v>53.18789267509513</v>
       </c>
     </row>
     <row r="675">
@@ -9135,7 +9135,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>53.00275774541674</v>
+        <v>55.16168536503547</v>
       </c>
     </row>
     <row r="676">
@@ -9148,7 +9148,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>55.26655090844426</v>
+        <v>57.45007468520216</v>
       </c>
     </row>
     <row r="677">
@@ -9187,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>22.132289714712</v>
+        <v>23.68357332860473</v>
       </c>
     </row>
     <row r="680">
@@ -9200,7 +9200,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>23.55105186138779</v>
+        <v>25.08407451602453</v>
       </c>
     </row>
     <row r="681">
@@ -9213,7 +9213,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>25.15523830041628</v>
+        <v>26.69806705661959</v>
       </c>
     </row>
     <row r="682">
@@ -9252,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>2.432749408785499</v>
+        <v>1.878190502277354</v>
       </c>
     </row>
     <row r="685">
@@ -9265,7 +9265,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>1.882450982510224</v>
+        <v>1.355698801975122</v>
       </c>
     </row>
     <row r="686">
@@ -9278,7 +9278,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>1.356639998310201</v>
+        <v>0.8360306906781272</v>
       </c>
     </row>
     <row r="687">
@@ -9317,7 +9317,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>20.91617908593969</v>
+        <v>17.79690903015864</v>
       </c>
     </row>
     <row r="690">
@@ -9330,7 +9330,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>17.82816740900576</v>
+        <v>14.66723790838515</v>
       </c>
     </row>
     <row r="691">
@@ -9343,7 +9343,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>14.65785873901263</v>
+        <v>11.50942927849411</v>
       </c>
     </row>
     <row r="692">
@@ -9356,7 +9356,7 @@
         <v>2024</v>
       </c>
       <c r="D692">
-        <v>57.50063350008139</v>
+        <v>57.50063350008138</v>
       </c>
     </row>
     <row r="693">
@@ -9382,7 +9382,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>55.88634989301584</v>
+        <v>54.28314044283619</v>
       </c>
     </row>
     <row r="695">
@@ -9395,7 +9395,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>54.28422171698178</v>
+        <v>52.69424897197922</v>
       </c>
     </row>
     <row r="696">
@@ -9408,7 +9408,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>52.69435454694894</v>
+        <v>51.1056742260314</v>
       </c>
     </row>
     <row r="697">
@@ -9421,7 +9421,7 @@
         <v>2024</v>
       </c>
       <c r="D697">
-        <v>39.55918764303696</v>
+        <v>39.55918764303695</v>
       </c>
     </row>
     <row r="698">
@@ -9447,7 +9447,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>38.1074464535663</v>
+        <v>36.66114397793008</v>
       </c>
     </row>
     <row r="700">
@@ -9460,7 +9460,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>36.66159830727241</v>
+        <v>35.22164320415527</v>
       </c>
     </row>
     <row r="701">
@@ -9473,7 +9473,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>35.22168115709002</v>
+        <v>33.7822562891847</v>
       </c>
     </row>
     <row r="702">
@@ -9486,7 +9486,7 @@
         <v>2024</v>
       </c>
       <c r="D702">
-        <v>72.30433131884882</v>
+        <v>72.30433131884881</v>
       </c>
     </row>
     <row r="703">
@@ -9512,7 +9512,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>75.15927596914281</v>
+        <v>77.82121364952981</v>
       </c>
     </row>
     <row r="705">
@@ -9525,7 +9525,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>77.73821283705395</v>
+        <v>80.04114192258226</v>
       </c>
     </row>
     <row r="706">
@@ -9538,7 +9538,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>80.00544821227236</v>
+        <v>82.15398906470502</v>
       </c>
     </row>
     <row r="707">
@@ -9577,7 +9577,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>21.2132507573339</v>
+        <v>22.21848773811836</v>
       </c>
     </row>
     <row r="710">
@@ -9590,7 +9590,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>21.87433670389955</v>
+        <v>22.66924418145944</v>
       </c>
     </row>
     <row r="711">
@@ -9603,7 +9603,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>22.91704069317153</v>
+        <v>23.86339015993682</v>
       </c>
     </row>
     <row r="712">
@@ -9616,7 +9616,7 @@
         <v>2024</v>
       </c>
       <c r="D712">
-        <v>78.23100870295282</v>
+        <v>78.23100870295279</v>
       </c>
     </row>
     <row r="713">
@@ -9642,7 +9642,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>79.47334762250649</v>
+        <v>80.72375170029922</v>
       </c>
     </row>
     <row r="715">
@@ -9655,7 +9655,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>80.72183892848328</v>
+        <v>81.97648262088316</v>
       </c>
     </row>
     <row r="716">
@@ -9668,7 +9668,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>81.97693626306989</v>
+        <v>83.2305744680273</v>
       </c>
     </row>
     <row r="717">
@@ -9681,7 +9681,7 @@
         <v>2024</v>
       </c>
       <c r="D717">
-        <v>50.61865145140401</v>
+        <v>50.61865145140398</v>
       </c>
     </row>
     <row r="718">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>51.26973410662463</v>
+        <v>52.67831683599599</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>52.29891306999675</v>
+        <v>53.70618834152036</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>53.89621765315547</v>
+        <v>55.30414778195006</v>
       </c>
     </row>
     <row r="722">
@@ -9746,7 +9746,7 @@
         <v>2024</v>
       </c>
       <c r="D722">
-        <v>28.48607404657862</v>
+        <v>28.48607404657861</v>
       </c>
     </row>
     <row r="723">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>28.70207447913174</v>
+        <v>28.97494002796125</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>28.96247578937242</v>
+        <v>29.26727797730065</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>29.2700100080037</v>
+        <v>29.5678120187492</v>
       </c>
     </row>
     <row r="727">
@@ -9811,7 +9811,7 @@
         <v>2024</v>
       </c>
       <c r="D727">
-        <v>59.2022282620627</v>
+        <v>59.20222826206269</v>
       </c>
     </row>
     <row r="728">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>58.68045133284442</v>
+        <v>58.15433595616752</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>58.15715251873445</v>
+        <v>57.63233181973279</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>57.63050327973799</v>
+        <v>57.10484206331368</v>
       </c>
     </row>
     <row r="732">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>66.41763774644859</v>
+        <v>67.3488739844928</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>66.34049769632811</v>
+        <v>66.28327613137056</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>67.27211976347645</v>
+        <v>68.18420917456604</v>
       </c>
     </row>
     <row r="737">
@@ -9941,7 +9941,7 @@
         <v>2024</v>
       </c>
       <c r="D737">
-        <v>70.95626918067411</v>
+        <v>70.9562691806741</v>
       </c>
     </row>
     <row r="738">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>72.45266056416733</v>
+        <v>74.02763842079514</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>74.00340750172028</v>
+        <v>75.60850999333292</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>75.61598122108744</v>
+        <v>77.21179524913427</v>
       </c>
     </row>
     <row r="742">
@@ -10006,7 +10006,7 @@
         <v>2024</v>
       </c>
       <c r="D742">
-        <v>88.03130666663873</v>
+        <v>88.03130666663871</v>
       </c>
     </row>
     <row r="743">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>90.34590554398422</v>
+        <v>92.51398418787113</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>92.57127344760249</v>
+        <v>94.70741037749352</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>94.68501033619482</v>
+        <v>96.83363644321986</v>
       </c>
     </row>
     <row r="747">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>64.88227581297987</v>
+        <v>64.23251770131291</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>64.24709959808007</v>
+        <v>63.54187046697339</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>63.5393581235788</v>
+        <v>62.84368620245009</v>
       </c>
     </row>
     <row r="752">
@@ -10136,7 +10136,7 @@
         <v>2024</v>
       </c>
       <c r="D752">
-        <v>44.77942899631731</v>
+        <v>44.77942899631729</v>
       </c>
     </row>
     <row r="753">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>44.76251185451347</v>
+        <v>44.74275716433439</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>44.74285499649855</v>
+        <v>44.72045842227255</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>44.72045504924377</v>
+        <v>44.69814956112436</v>
       </c>
     </row>
     <row r="757">
@@ -10201,7 +10201,7 @@
         <v>2024</v>
       </c>
       <c r="D757">
-        <v>34.07061117444113</v>
+        <v>34.07061117444112</v>
       </c>
     </row>
     <row r="758">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>33.93352764418388</v>
+        <v>33.17145006718575</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>33.5657048540023</v>
+        <v>32.96714280389638</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>32.71844149587864</v>
+        <v>32.01673161655378</v>
       </c>
     </row>
     <row r="762">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>33.17837967945241</v>
+        <v>32.64368841193886</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>32.64368635922156</v>
+        <v>32.10914217613151</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>32.10914220400142</v>
+        <v>31.57459602393391</v>
       </c>
     </row>
     <row r="767">
@@ -10331,7 +10331,7 @@
         <v>2024</v>
       </c>
       <c r="D767">
-        <v>45.4266757479536</v>
+        <v>45.42667574795358</v>
       </c>
     </row>
     <row r="768">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>44.02187855226029</v>
+        <v>43.8010165094801</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>42.9536359659003</v>
+        <v>42.22194798887364</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>42.82844555241908</v>
+        <v>42.46237215890348</v>
       </c>
     </row>
     <row r="772">
@@ -10396,7 +10396,7 @@
         <v>2024</v>
       </c>
       <c r="D772">
-        <v>55.05644358551569</v>
+        <v>55.05644358551568</v>
       </c>
     </row>
     <row r="773">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>55.4759450385982</v>
+        <v>55.68067761930187</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>55.56275362240063</v>
+        <v>55.31686933692296</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>55.2521203400542</v>
+        <v>54.75881406393777</v>
       </c>
     </row>
     <row r="777">
@@ -10487,7 +10487,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>58.30910095750405</v>
+        <v>56.92061211807879</v>
       </c>
     </row>
     <row r="780">
@@ -10500,7 +10500,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>56.92176119652976</v>
+        <v>55.52142575687809</v>
       </c>
     </row>
     <row r="781">
@@ -10513,7 +10513,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>55.52133240912567</v>
+        <v>54.12195935242009</v>
       </c>
     </row>
     <row r="782">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>44.66538547106169</v>
+        <v>42.80307949124654</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>42.94446290837008</v>
+        <v>41.58762521657623</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>41.67738336722484</v>
+        <v>40.64144539385177</v>
       </c>
     </row>
     <row r="787">
@@ -10591,7 +10591,7 @@
         <v>2024</v>
       </c>
       <c r="D787">
-        <v>83.62020006343781</v>
+        <v>83.62020006343778</v>
       </c>
     </row>
     <row r="788">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>85.45134984480116</v>
+        <v>87.12650110695338</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>87.07398585250405</v>
+        <v>88.48810808654645</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>88.47042938059575</v>
+        <v>89.79667894828739</v>
       </c>
     </row>
     <row r="792">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>35.26514863069872</v>
+        <v>32.78938098545235</v>
       </c>
     </row>
     <row r="795">
@@ -10695,7 +10695,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>33.09464490825102</v>
+        <v>30.74684811049517</v>
       </c>
     </row>
     <row r="796">
@@ -10708,7 +10708,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>30.55373918672447</v>
+        <v>28.12498846422587</v>
       </c>
     </row>
     <row r="797">
@@ -10721,7 +10721,7 @@
         <v>2024</v>
       </c>
       <c r="D797">
-        <v>73.82866020480907</v>
+        <v>73.82866020480904</v>
       </c>
     </row>
     <row r="798">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>74.68703331989924</v>
+        <v>75.50402944197131</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>75.51914524121726</v>
+        <v>76.32499596876313</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>76.31947388099944</v>
+        <v>77.12939623226387</v>
       </c>
     </row>
     <row r="802">
@@ -10786,7 +10786,7 @@
         <v>2024</v>
       </c>
       <c r="D802">
-        <v>85.59923491119088</v>
+        <v>85.59923491119086</v>
       </c>
     </row>
     <row r="803">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>84.90591595705256</v>
+        <v>85.71122747579868</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>84.68608747929393</v>
+        <v>84.939749477915</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>85.64099773854262</v>
+        <v>86.2720162619142</v>
       </c>
     </row>
     <row r="807">
@@ -10851,7 +10851,7 @@
         <v>2024</v>
       </c>
       <c r="D807">
-        <v>51.80329802942769</v>
+        <v>51.80329802942771</v>
       </c>
     </row>
     <row r="808">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>51.42435267101041</v>
+        <v>51.15834959539224</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>51.11131521256043</v>
+        <v>50.86418565407776</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>50.88377294338644</v>
+        <v>50.62878358068932</v>
       </c>
     </row>
     <row r="812">
@@ -10916,7 +10916,7 @@
         <v>2024</v>
       </c>
       <c r="D812">
-        <v>38.59657822951705</v>
+        <v>38.59657822951704</v>
       </c>
     </row>
     <row r="813">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>35.82574280239682</v>
+        <v>33.0810193883657</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>33.08562515922087</v>
+        <v>30.3762252999892</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>30.37703768948586</v>
+        <v>27.67386838010268</v>
       </c>
     </row>
     <row r="817">
@@ -10981,7 +10981,7 @@
         <v>2024</v>
       </c>
       <c r="D817">
-        <v>69.98215937446899</v>
+        <v>69.98215937446898</v>
       </c>
     </row>
     <row r="818">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>69.1531976839989</v>
+        <v>68.59769568011524</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>68.39263724642986</v>
+        <v>67.70047806176188</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>67.85424464341197</v>
+        <v>67.26456018835881</v>
       </c>
     </row>
     <row r="822">
@@ -11046,7 +11046,7 @@
         <v>2024</v>
       </c>
       <c r="D822">
-        <v>92.94175528542988</v>
+        <v>92.94175528542986</v>
       </c>
     </row>
     <row r="823">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>94.16456225823605</v>
+        <v>95.44094596850573</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>95.42758086818948</v>
+        <v>96.73081111529022</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>96.73414513514511</v>
+        <v>98.03067832163937</v>
       </c>
     </row>
     <row r="827">
@@ -11111,7 +11111,7 @@
         <v>2024</v>
       </c>
       <c r="D827">
-        <v>76.75536521677762</v>
+        <v>76.75536521677759</v>
       </c>
     </row>
     <row r="828">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>77.4952372496673</v>
+        <v>78.44403492042385</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>78.3761496471103</v>
+        <v>79.39810240910661</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>79.42016006741943</v>
+        <v>80.41834287272786</v>
       </c>
     </row>
     <row r="832">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>67.43547011569832</v>
+        <v>67.97567140917928</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>67.91358602442934</v>
+        <v>68.18938937587706</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>68.16190115850868</v>
+        <v>68.3206426904697</v>
       </c>
     </row>
     <row r="837">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>43.72120582889701</v>
+        <v>41.60699278885193</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>41.52380807134958</v>
+        <v>39.5255752145287</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>39.55008276396104</v>
+        <v>37.51768028850249</v>
       </c>
     </row>
     <row r="842">
@@ -11306,7 +11306,7 @@
         <v>2024</v>
       </c>
       <c r="D842">
-        <v>41.14104720064982</v>
+        <v>41.14104720064981</v>
       </c>
     </row>
     <row r="843">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>38.2285981081529</v>
+        <v>35.3102844569007</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>35.31056106163542</v>
+        <v>32.38693606109739</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>32.38692301490202</v>
+        <v>29.46354852670796</v>
       </c>
     </row>
     <row r="847">
@@ -11371,7 +11371,7 @@
         <v>2024</v>
       </c>
       <c r="D847">
-        <v>86.6857243326739</v>
+        <v>86.68572433267391</v>
       </c>
     </row>
     <row r="848">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>86.54547182401886</v>
+        <v>86.21197303133134</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>86.36589236544727</v>
+        <v>86.14698595695911</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>86.02439026756046</v>
+        <v>85.71421181439095</v>
       </c>
     </row>
     <row r="852">
@@ -11436,7 +11436,7 @@
         <v>2024</v>
       </c>
       <c r="D852">
-        <v>66.90961343500048</v>
+        <v>66.90961343500049</v>
       </c>
     </row>
     <row r="853">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>66.93175847746173</v>
+        <v>66.95388233632343</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>66.95387904904037</v>
+        <v>66.9759751497364</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>66.97597463961394</v>
+        <v>66.998066432782</v>
       </c>
     </row>
     <row r="857">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>55.21337569503172</v>
+        <v>50.59439308461512</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>50.71774029677604</v>
+        <v>46.20025078525141</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>46.09546844457492</v>
+        <v>41.49176146385821</v>
       </c>
     </row>
     <row r="862">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>42.86089187962772</v>
+        <v>42.28400276791797</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>41.87645753065727</v>
+        <v>40.98007987227596</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>41.31521400126223</v>
+        <v>40.6815593635928</v>
       </c>
     </row>
     <row r="867">
@@ -11631,7 +11631,7 @@
         <v>2024</v>
       </c>
       <c r="D867">
-        <v>78.30860575158734</v>
+        <v>78.30860575158732</v>
       </c>
     </row>
     <row r="868">
@@ -11657,7 +11657,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>78.22565859499335</v>
+        <v>78.14842130721519</v>
       </c>
     </row>
     <row r="870">
@@ -11670,7 +11670,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>78.14895258198429</v>
+        <v>78.07848771256013</v>
       </c>
     </row>
     <row r="871">
@@ -11683,7 +11683,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>78.07853714502336</v>
+        <v>78.00870241529476</v>
       </c>
     </row>
     <row r="872">
@@ -11696,7 +11696,7 @@
         <v>2024</v>
       </c>
       <c r="D872">
-        <v>70.22843632027549</v>
+        <v>70.22843632027548</v>
       </c>
     </row>
     <row r="873">
@@ -11722,7 +11722,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>69.78435263190615</v>
+        <v>69.36211530270363</v>
       </c>
     </row>
     <row r="875">
@@ -11735,7 +11735,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>69.35184490849298</v>
+        <v>68.93091315003599</v>
       </c>
     </row>
     <row r="876">
@@ -11748,7 +11748,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>68.93574146016476</v>
+        <v>68.5141959277547</v>
       </c>
     </row>
     <row r="877">
@@ -11761,7 +11761,7 @@
         <v>2024</v>
       </c>
       <c r="D877">
-        <v>90.53683807284561</v>
+        <v>90.53683807284558</v>
       </c>
     </row>
     <row r="878">
@@ -11787,7 +11787,7 @@
         <v>2026</v>
       </c>
       <c r="D879">
-        <v>92.18073556118345</v>
+        <v>94.25944833457463</v>
       </c>
     </row>
     <row r="880">
@@ -11800,7 +11800,7 @@
         <v>2027</v>
       </c>
       <c r="D880">
-        <v>94.10009753806462</v>
+        <v>96.29492400348904</v>
       </c>
     </row>
     <row r="881">
@@ -11813,7 +11813,7 @@
         <v>2028</v>
       </c>
       <c r="D881">
-        <v>96.35332277009464</v>
+        <v>98.50559597222028</v>
       </c>
     </row>
     <row r="882">
@@ -11852,7 +11852,7 @@
         <v>2026</v>
       </c>
       <c r="D884">
-        <v>66.49541937539828</v>
+        <v>65.22097594387695</v>
       </c>
     </row>
     <row r="885">
@@ -11865,7 +11865,7 @@
         <v>2027</v>
       </c>
       <c r="D885">
-        <v>65.13262021957414</v>
+        <v>63.87341949708918</v>
       </c>
     </row>
     <row r="886">
@@ -11878,7 +11878,7 @@
         <v>2028</v>
       </c>
       <c r="D886">
-        <v>63.91408928050505</v>
+        <v>62.64787240054899</v>
       </c>
     </row>
     <row r="887">
@@ -11917,7 +11917,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>43.86111123549772</v>
+        <v>44.93833304657662</v>
       </c>
     </row>
     <row r="890">
@@ -11930,7 +11930,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>44.93865440209709</v>
+        <v>46.02178673291405</v>
       </c>
     </row>
     <row r="891">
@@ -11943,7 +11943,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>46.02180633677145</v>
+        <v>47.1052992308237</v>
       </c>
     </row>
     <row r="892">
@@ -11982,7 +11982,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>18.46685553053259</v>
+        <v>18.92598555530285</v>
       </c>
     </row>
     <row r="895">
@@ -11995,7 +11995,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>19.07811932489487</v>
+        <v>19.5681076208443</v>
       </c>
     </row>
     <row r="896">
@@ -12008,7 +12008,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>19.48345546541749</v>
+        <v>19.95627322010532</v>
       </c>
     </row>
     <row r="897">
@@ -12047,7 +12047,7 @@
         <v>2026</v>
       </c>
       <c r="D899">
-        <v>13.15268109805286</v>
+        <v>10.98750587615093</v>
       </c>
     </row>
     <row r="900">
@@ -12060,7 +12060,7 @@
         <v>2027</v>
       </c>
       <c r="D900">
-        <v>10.98446552855196</v>
+        <v>8.827195260069843</v>
       </c>
     </row>
     <row r="901">
@@ -12073,7 +12073,7 @@
         <v>2028</v>
       </c>
       <c r="D901">
-        <v>8.827856202853063</v>
+        <v>6.66886747233842</v>
       </c>
     </row>
     <row r="902">
@@ -12112,7 +12112,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>24.67325954007789</v>
+        <v>25.13819198580114</v>
       </c>
     </row>
     <row r="905">
@@ -12125,7 +12125,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>25.13682793657087</v>
+        <v>25.61595698874779</v>
       </c>
     </row>
     <row r="906">
@@ -12138,7 +12138,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>25.61606692450809</v>
+        <v>26.09405179897534</v>
       </c>
     </row>
     <row r="907">
@@ -12177,7 +12177,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>15.3278895808253</v>
+        <v>11.2315262273206</v>
       </c>
     </row>
     <row r="910">
@@ -12190,7 +12190,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>11.1380696623231</v>
+        <v>7.098981724379144</v>
       </c>
     </row>
     <row r="911">
@@ -12203,7 +12203,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>7.134749698348824</v>
+        <v>3.073741143346731</v>
       </c>
     </row>
     <row r="912">
@@ -12242,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>17.7172246085324</v>
+        <v>17.69811056729965</v>
       </c>
     </row>
     <row r="915">
@@ -12255,7 +12255,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>17.66987370934016</v>
+        <v>17.50592963393148</v>
       </c>
     </row>
     <row r="916">
@@ -12268,7 +12268,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>17.49690571619527</v>
+        <v>17.28667694735468</v>
       </c>
     </row>
     <row r="917">
@@ -12281,7 +12281,7 @@
         <v>2024</v>
       </c>
       <c r="D917">
-        <v>13.51659680278183</v>
+        <v>13.51659680278182</v>
       </c>
     </row>
     <row r="918">
@@ -12307,7 +12307,7 @@
         <v>2026</v>
       </c>
       <c r="D919">
-        <v>10.43067343015796</v>
+        <v>7.29975634488342</v>
       </c>
     </row>
     <row r="920">
@@ -12320,7 +12320,7 @@
         <v>2027</v>
       </c>
       <c r="D920">
-        <v>7.274558385105315</v>
+        <v>4.048251667623902</v>
       </c>
     </row>
     <row r="921">
@@ -12333,7 +12333,7 @@
         <v>2028</v>
       </c>
       <c r="D921">
-        <v>4.03413998091095</v>
+        <v>0.75441193022553</v>
       </c>
     </row>
     <row r="922">
@@ -12372,7 +12372,7 @@
         <v>2026</v>
       </c>
       <c r="D924">
-        <v>16.9358735147589</v>
+        <v>16.56117570891661</v>
       </c>
     </row>
     <row r="925">
@@ -12385,7 +12385,7 @@
         <v>2027</v>
       </c>
       <c r="D925">
-        <v>16.51959946161573</v>
+        <v>16.12710613600625</v>
       </c>
     </row>
     <row r="926">
@@ -12398,7 +12398,7 @@
         <v>2028</v>
       </c>
       <c r="D926">
-        <v>16.15355448897852</v>
+        <v>15.7723816220127</v>
       </c>
     </row>
     <row r="927">
@@ -12437,7 +12437,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>22.06485885911339</v>
+        <v>21.02378976245124</v>
       </c>
     </row>
     <row r="930">
@@ -12450,7 +12450,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>21.15322194446395</v>
+        <v>20.08139982247343</v>
       </c>
     </row>
     <row r="931">
@@ -12463,7 +12463,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>20.02355561022515</v>
+        <v>18.96547724575079</v>
       </c>
     </row>
     <row r="932">
@@ -12476,7 +12476,7 @@
         <v>2024</v>
       </c>
       <c r="D932">
-        <v>25.37035960723257</v>
+        <v>25.37035960723255</v>
       </c>
     </row>
     <row r="933">
@@ -12502,7 +12502,7 @@
         <v>2026</v>
       </c>
       <c r="D934">
-        <v>23.37289141591303</v>
+        <v>21.60662492605064</v>
       </c>
     </row>
     <row r="935">
@@ -12515,7 +12515,7 @@
         <v>2027</v>
       </c>
       <c r="D935">
-        <v>21.47092326465065</v>
+        <v>19.66445515344541</v>
       </c>
     </row>
     <row r="936">
@@ -12528,7 +12528,7 @@
         <v>2028</v>
       </c>
       <c r="D936">
-        <v>19.74410396567585</v>
+        <v>17.9612318175315</v>
       </c>
     </row>
     <row r="937">
@@ -12567,7 +12567,7 @@
         <v>2026</v>
       </c>
       <c r="D939">
-        <v>38.59602567973144</v>
+        <v>36.95047552426982</v>
       </c>
     </row>
     <row r="940">
@@ -12580,7 +12580,7 @@
         <v>2027</v>
       </c>
       <c r="D940">
-        <v>36.93756927306055</v>
+        <v>35.34428046153714</v>
       </c>
     </row>
     <row r="941">
@@ -12593,7 +12593,7 @@
         <v>2028</v>
       </c>
       <c r="D941">
-        <v>35.34641397138775</v>
+        <v>33.74448592835629</v>
       </c>
     </row>
     <row r="942">
@@ -12606,7 +12606,7 @@
         <v>2024</v>
       </c>
       <c r="D942">
-        <v>26.8041042250095</v>
+        <v>26.80410422500951</v>
       </c>
     </row>
     <row r="943">
@@ -12632,7 +12632,7 @@
         <v>2026</v>
       </c>
       <c r="D944">
-        <v>23.82002022500361</v>
+        <v>20.92766075788996</v>
       </c>
     </row>
     <row r="945">
@@ -12645,7 +12645,7 @@
         <v>2027</v>
       </c>
       <c r="D945">
-        <v>20.95350748884321</v>
+        <v>18.2045660165283</v>
       </c>
     </row>
     <row r="946">
@@ -12658,7 +12658,7 @@
         <v>2028</v>
       </c>
       <c r="D946">
-        <v>18.21184927521498</v>
+        <v>15.5033210512267</v>
       </c>
     </row>
     <row r="947">
@@ -12697,7 +12697,7 @@
         <v>2026</v>
       </c>
       <c r="D949">
-        <v>52.28264275356326</v>
+        <v>50.12833126147412</v>
       </c>
     </row>
     <row r="950">
@@ -12710,7 +12710,7 @@
         <v>2027</v>
       </c>
       <c r="D950">
-        <v>50.12845597110925</v>
+        <v>47.97634089944292</v>
       </c>
     </row>
     <row r="951">
@@ -12723,7 +12723,7 @@
         <v>2028</v>
       </c>
       <c r="D951">
-        <v>47.97634888736479</v>
+        <v>45.82437450117733</v>
       </c>
     </row>
     <row r="952">
@@ -12736,7 +12736,7 @@
         <v>2024</v>
       </c>
       <c r="D952">
-        <v>44.75153733380408</v>
+        <v>44.75153733380407</v>
       </c>
     </row>
     <row r="953">
@@ -12762,7 +12762,7 @@
         <v>2026</v>
       </c>
       <c r="D954">
-        <v>42.63286854612004</v>
+        <v>40.42644772335566</v>
       </c>
     </row>
     <row r="955">
@@ -12775,7 +12775,7 @@
         <v>2027</v>
       </c>
       <c r="D955">
-        <v>40.46676003376982</v>
+        <v>38.25321179675345</v>
       </c>
     </row>
     <row r="956">
@@ -12788,7 +12788,7 @@
         <v>2028</v>
       </c>
       <c r="D956">
-        <v>38.23469276902446</v>
+        <v>36.02441878696428</v>
       </c>
     </row>
     <row r="957">
@@ -12801,7 +12801,7 @@
         <v>2024</v>
       </c>
       <c r="D957">
-        <v>79.43137961007255</v>
+        <v>79.43137961007254</v>
       </c>
     </row>
     <row r="958">
@@ -12827,7 +12827,7 @@
         <v>2026</v>
       </c>
       <c r="D959">
-        <v>78.12409747034587</v>
+        <v>77.70297536395063</v>
       </c>
     </row>
     <row r="960">
@@ -12840,7 +12840,7 @@
         <v>2027</v>
       </c>
       <c r="D960">
-        <v>77.22341461824669</v>
+        <v>76.729331053775</v>
       </c>
     </row>
     <row r="961">
@@ -12853,7 +12853,7 @@
         <v>2028</v>
       </c>
       <c r="D961">
-        <v>76.9888536006851</v>
+        <v>76.53425438432969</v>
       </c>
     </row>
     <row r="962">
@@ -12866,7 +12866,7 @@
         <v>2024</v>
       </c>
       <c r="D962">
-        <v>28.60275604981868</v>
+        <v>28.60275604981867</v>
       </c>
     </row>
     <row r="963">
@@ -12892,7 +12892,7 @@
         <v>2026</v>
       </c>
       <c r="D964">
-        <v>24.98804302234578</v>
+        <v>21.42569027518668</v>
       </c>
     </row>
     <row r="965">
@@ -12905,7 +12905,7 @@
         <v>2027</v>
       </c>
       <c r="D965">
-        <v>21.40979926138683</v>
+        <v>17.86802476694184</v>
       </c>
     </row>
     <row r="966">
@@ -12918,7 +12918,7 @@
         <v>2028</v>
       </c>
       <c r="D966">
-        <v>17.87284758909011</v>
+        <v>14.32482772514182</v>
       </c>
     </row>
     <row r="967">
@@ -12931,7 +12931,7 @@
         <v>2024</v>
       </c>
       <c r="D967">
-        <v>54.23860949786785</v>
+        <v>54.23860949786784</v>
       </c>
     </row>
     <row r="968">
@@ -12957,7 +12957,7 @@
         <v>2026</v>
       </c>
       <c r="D969">
-        <v>54.65099186569486</v>
+        <v>54.37086998434386</v>
       </c>
     </row>
     <row r="970">
@@ -12970,7 +12970,7 @@
         <v>2027</v>
       </c>
       <c r="D970">
-        <v>54.78079492316897</v>
+        <v>54.62801867029017</v>
       </c>
     </row>
     <row r="971">
@@ -12983,7 +12983,7 @@
         <v>2028</v>
       </c>
       <c r="D971">
-        <v>54.38536534986617</v>
+        <v>54.1572073949645</v>
       </c>
     </row>
     <row r="972">
@@ -12996,7 +12996,7 @@
         <v>2024</v>
       </c>
       <c r="D972">
-        <v>86.88239805081626</v>
+        <v>86.88239805081625</v>
       </c>
     </row>
     <row r="973">
@@ -13022,7 +13022,7 @@
         <v>2026</v>
       </c>
       <c r="D974">
-        <v>85.9899052494665</v>
+        <v>85.10740240457731</v>
       </c>
     </row>
     <row r="975">
@@ -13035,7 +13035,7 @@
         <v>2027</v>
       </c>
       <c r="D975">
-        <v>85.10562089452982</v>
+        <v>84.22954498600626</v>
       </c>
     </row>
     <row r="976">
@@ -13048,7 +13048,7 @@
         <v>2028</v>
       </c>
       <c r="D976">
-        <v>84.22986268289129</v>
+        <v>83.35264065809034</v>
       </c>
     </row>
     <row r="977">
@@ -13061,7 +13061,7 @@
         <v>2024</v>
       </c>
       <c r="D977">
-        <v>85.8480850834826</v>
+        <v>85.84808508348259</v>
       </c>
     </row>
     <row r="978">
@@ -13087,7 +13087,7 @@
         <v>2026</v>
       </c>
       <c r="D979">
-        <v>86.26303352522729</v>
+        <v>86.74708506343231</v>
       </c>
     </row>
     <row r="980">
@@ -13100,7 +13100,7 @@
         <v>2027</v>
       </c>
       <c r="D980">
-        <v>86.7702194216954</v>
+        <v>87.36964277288692</v>
       </c>
     </row>
     <row r="981">
@@ -13113,7 +13113,7 @@
         <v>2028</v>
       </c>
       <c r="D981">
-        <v>87.37738770125712</v>
+        <v>88.01543526745213</v>
       </c>
     </row>
     <row r="982">
@@ -13126,7 +13126,7 @@
         <v>2024</v>
       </c>
       <c r="D982">
-        <v>79.16552703380985</v>
+        <v>79.16552703380982</v>
       </c>
     </row>
     <row r="983">
@@ -13152,7 +13152,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>78.01010245704749</v>
+        <v>77.09798024220279</v>
       </c>
     </row>
     <row r="985">
@@ -13165,7 +13165,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>77.00519214687294</v>
+        <v>76.15079610328617</v>
       </c>
     </row>
     <row r="986">
@@ -13178,7 +13178,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>76.18618265098378</v>
+        <v>75.30977160746239</v>
       </c>
     </row>
     <row r="987">
@@ -13217,7 +13217,7 @@
         <v>2026</v>
       </c>
       <c r="D989">
-        <v>68.05903343068313</v>
+        <v>65.93422359882149</v>
       </c>
     </row>
     <row r="990">
@@ -13230,7 +13230,7 @@
         <v>2027</v>
       </c>
       <c r="D990">
-        <v>65.8854611710513</v>
+        <v>63.81357011411971</v>
       </c>
     </row>
     <row r="991">
@@ -13243,7 +13243,7 @@
         <v>2028</v>
       </c>
       <c r="D991">
-        <v>63.8293751990848</v>
+        <v>61.74033188431321</v>
       </c>
     </row>
     <row r="992">
@@ -13256,7 +13256,7 @@
         <v>2024</v>
       </c>
       <c r="D992">
-        <v>75.87900964178705</v>
+        <v>75.87900964178704</v>
       </c>
     </row>
     <row r="993">
@@ -13282,7 +13282,7 @@
         <v>2026</v>
       </c>
       <c r="D994">
-        <v>76.65754556087674</v>
+        <v>77.43686867023952</v>
       </c>
     </row>
     <row r="995">
@@ -13295,7 +13295,7 @@
         <v>2027</v>
       </c>
       <c r="D995">
-        <v>77.43660287253915</v>
+        <v>78.21618157677429</v>
       </c>
     </row>
     <row r="996">
@@ -13308,7 +13308,7 @@
         <v>2028</v>
       </c>
       <c r="D996">
-        <v>78.21627132434858</v>
+        <v>78.99576372603195</v>
       </c>
     </row>
     <row r="997">
@@ -13321,7 +13321,7 @@
         <v>2024</v>
       </c>
       <c r="D997">
-        <v>23.90401647019363</v>
+        <v>23.90401647019362</v>
       </c>
     </row>
     <row r="998">
@@ -13347,7 +13347,7 @@
         <v>2026</v>
       </c>
       <c r="D999">
-        <v>19.28448613082374</v>
+        <v>15.06262098035602</v>
       </c>
     </row>
     <row r="1000">
@@ -13360,7 +13360,7 @@
         <v>2027</v>
       </c>
       <c r="D1000">
-        <v>14.70241104988554</v>
+        <v>10.15779122737903</v>
       </c>
     </row>
     <row r="1001">
@@ -13373,7 +13373,7 @@
         <v>2028</v>
       </c>
       <c r="D1001">
-        <v>10.48407373243749</v>
+        <v>6.231808989577416</v>
       </c>
     </row>
     <row r="1002">
@@ -13386,7 +13386,7 @@
         <v>2024</v>
       </c>
       <c r="D1002">
-        <v>74.34904737257474</v>
+        <v>74.34904737257473</v>
       </c>
     </row>
     <row r="1003">
@@ -13412,7 +13412,7 @@
         <v>2026</v>
       </c>
       <c r="D1004">
-        <v>72.46745662583501</v>
+        <v>72.58770306499085</v>
       </c>
     </row>
     <row r="1005">
@@ -13425,7 +13425,7 @@
         <v>2027</v>
       </c>
       <c r="D1005">
-        <v>70.69620594499314</v>
+        <v>69.03529533004914</v>
       </c>
     </row>
     <row r="1006">
@@ -13438,7 +13438,7 @@
         <v>2028</v>
       </c>
       <c r="D1006">
-        <v>70.82253426244962</v>
+        <v>70.84460439230892</v>
       </c>
     </row>
     <row r="1007">
@@ -13451,7 +13451,7 @@
         <v>2024</v>
       </c>
       <c r="D1007">
-        <v>51.22604949506189</v>
+        <v>51.22604949506187</v>
       </c>
     </row>
     <row r="1008">
@@ -13477,7 +13477,7 @@
         <v>2026</v>
       </c>
       <c r="D1009">
-        <v>49.31631339609086</v>
+        <v>47.39743183467393</v>
       </c>
     </row>
     <row r="1010">
@@ -13490,7 +13490,7 @@
         <v>2027</v>
       </c>
       <c r="D1010">
-        <v>47.40180262902433</v>
+        <v>45.48251719386232</v>
       </c>
     </row>
     <row r="1011">
@@ -13503,7 +13503,7 @@
         <v>2028</v>
       </c>
       <c r="D1011">
-        <v>45.48042830624549</v>
+        <v>43.5613358902002</v>
       </c>
     </row>
     <row r="1012">
@@ -13542,7 +13542,7 @@
         <v>2026</v>
       </c>
       <c r="D1014">
-        <v>34.01540084851178</v>
+        <v>31.82921862370404</v>
       </c>
     </row>
     <row r="1015">
@@ -13555,7 +13555,7 @@
         <v>2027</v>
       </c>
       <c r="D1015">
-        <v>31.68136162573229</v>
+        <v>29.6118805829171</v>
       </c>
     </row>
     <row r="1016">
@@ -13568,7 +13568,7 @@
         <v>2028</v>
       </c>
       <c r="D1016">
-        <v>29.66488952395225</v>
+        <v>27.55356936523564</v>
       </c>
     </row>
     <row r="1017">
@@ -13581,7 +13581,7 @@
         <v>2024</v>
       </c>
       <c r="D1017">
-        <v>72.27910227110445</v>
+        <v>72.27910227110443</v>
       </c>
     </row>
     <row r="1018">
@@ -13607,7 +13607,7 @@
         <v>2026</v>
       </c>
       <c r="D1019">
-        <v>69.56246857891189</v>
+        <v>67.14865988230579</v>
       </c>
     </row>
     <row r="1020">
@@ -13620,7 +13620,7 @@
         <v>2027</v>
       </c>
       <c r="D1020">
-        <v>66.99222643862521</v>
+        <v>64.56837585024438</v>
       </c>
     </row>
     <row r="1021">
@@ -13633,7 +13633,7 @@
         <v>2028</v>
       </c>
       <c r="D1021">
-        <v>64.6491862940929</v>
+        <v>62.23052314972854</v>
       </c>
     </row>
     <row r="1022">
@@ -13646,7 +13646,7 @@
         <v>2024</v>
       </c>
       <c r="D1022">
-        <v>76.88410505812261</v>
+        <v>76.8841050581226</v>
       </c>
     </row>
     <row r="1023">
@@ -13672,7 +13672,7 @@
         <v>2026</v>
       </c>
       <c r="D1024">
-        <v>76.45652000993333</v>
+        <v>76.19964389350251</v>
       </c>
     </row>
     <row r="1025">
@@ -13685,7 +13685,7 @@
         <v>2027</v>
       </c>
       <c r="D1025">
-        <v>76.08076983145708</v>
+        <v>75.75685452269386</v>
       </c>
     </row>
     <row r="1026">
@@ -13698,7 +13698,7 @@
         <v>2028</v>
       </c>
       <c r="D1026">
-        <v>75.83963310071914</v>
+        <v>75.56240088596107</v>
       </c>
     </row>
     <row r="1027">
@@ -13711,7 +13711,7 @@
         <v>2024</v>
       </c>
       <c r="D1027">
-        <v>45.66053684455816</v>
+        <v>45.66053684455817</v>
       </c>
     </row>
     <row r="1028">
@@ -13737,7 +13737,7 @@
         <v>2026</v>
       </c>
       <c r="D1029">
-        <v>41.59269549483328</v>
+        <v>37.79880810606962</v>
       </c>
     </row>
     <row r="1030">
@@ -13750,7 +13750,7 @@
         <v>2027</v>
       </c>
       <c r="D1030">
-        <v>37.67406655762716</v>
+        <v>33.90465003293981</v>
       </c>
     </row>
     <row r="1031">
@@ -13763,7 +13763,7 @@
         <v>2028</v>
       </c>
       <c r="D1031">
-        <v>33.96144955448433</v>
+        <v>30.18089052444355</v>
       </c>
     </row>
     <row r="1032">
@@ -13776,7 +13776,7 @@
         <v>2024</v>
       </c>
       <c r="D1032">
-        <v>89.93917123347674</v>
+        <v>89.93917123347676</v>
       </c>
     </row>
     <row r="1033">
@@ -13802,7 +13802,7 @@
         <v>2026</v>
       </c>
       <c r="D1034">
-        <v>87.17760945053926</v>
+        <v>85.62108644141651</v>
       </c>
     </row>
     <row r="1035">
@@ -13815,7 +13815,7 @@
         <v>2027</v>
       </c>
       <c r="D1035">
-        <v>84.826378059468</v>
+        <v>82.88547706026293</v>
       </c>
     </row>
     <row r="1036">
@@ -13828,7 +13828,7 @@
         <v>2028</v>
       </c>
       <c r="D1036">
-        <v>83.40957755068943</v>
+        <v>81.72216915038884</v>
       </c>
     </row>
     <row r="1037">
@@ -13841,7 +13841,7 @@
         <v>2024</v>
       </c>
       <c r="D1037">
-        <v>79.4285812137377</v>
+        <v>79.42858121373769</v>
       </c>
     </row>
     <row r="1038">
@@ -13867,7 +13867,7 @@
         <v>2026</v>
       </c>
       <c r="D1039">
-        <v>79.73089642912761</v>
+        <v>80.033211644522</v>
       </c>
     </row>
     <row r="1040">
@@ -13880,7 +13880,7 @@
         <v>2027</v>
       </c>
       <c r="D1040">
-        <v>80.0332116445221</v>
+        <v>80.33552685992112</v>
       </c>
     </row>
     <row r="1041">
@@ -13893,7 +13893,7 @@
         <v>2028</v>
       </c>
       <c r="D1041">
-        <v>80.33552685992112</v>
+        <v>80.63784207532025</v>
       </c>
     </row>
     <row r="1042">
@@ -13932,7 +13932,7 @@
         <v>2026</v>
       </c>
       <c r="D1044">
-        <v>69.94540464016059</v>
+        <v>68.30732145669447</v>
       </c>
     </row>
     <row r="1045">
@@ -13945,7 +13945,7 @@
         <v>2027</v>
       </c>
       <c r="D1045">
-        <v>68.30738931965031</v>
+        <v>66.66967438424103</v>
       </c>
     </row>
     <row r="1046">
@@ -13958,7 +13958,7 @@
         <v>2028</v>
       </c>
       <c r="D1046">
-        <v>66.66969419044391</v>
+        <v>65.0320867303962</v>
       </c>
     </row>
     <row r="1047">
@@ -13971,7 +13971,7 @@
         <v>2024</v>
       </c>
       <c r="D1047">
-        <v>54.96264998265833</v>
+        <v>54.96264998265832</v>
       </c>
     </row>
     <row r="1048">
@@ -13997,7 +13997,7 @@
         <v>2026</v>
       </c>
       <c r="D1049">
-        <v>51.21522997008813</v>
+        <v>47.06203077162209</v>
       </c>
     </row>
     <row r="1050">
@@ -14010,7 +14010,7 @@
         <v>2027</v>
       </c>
       <c r="D1050">
-        <v>47.31465558584051</v>
+        <v>43.26092682991547</v>
       </c>
     </row>
     <row r="1051">
@@ -14023,7 +14023,7 @@
         <v>2028</v>
       </c>
       <c r="D1051">
-        <v>43.10365090503529</v>
+        <v>38.98799511356834</v>
       </c>
     </row>
     <row r="1052">
@@ -14036,7 +14036,7 @@
         <v>2024</v>
       </c>
       <c r="D1052">
-        <v>65.58840626071105</v>
+        <v>65.58840626071104</v>
       </c>
     </row>
     <row r="1053">
@@ -14062,7 +14062,7 @@
         <v>2026</v>
       </c>
       <c r="D1054">
-        <v>64.13198652106141</v>
+        <v>62.35087206219353</v>
       </c>
     </row>
     <row r="1055">
@@ -14075,7 +14075,7 @@
         <v>2027</v>
       </c>
       <c r="D1055">
-        <v>62.60469552472457</v>
+        <v>61.00653327170052</v>
       </c>
     </row>
     <row r="1056">
@@ -14088,7 +14088,7 @@
         <v>2028</v>
       </c>
       <c r="D1056">
-        <v>60.80811196603111</v>
+        <v>59.06693056419932</v>
       </c>
     </row>
     <row r="1057">
@@ -14101,7 +14101,7 @@
         <v>2024</v>
       </c>
       <c r="D1057">
-        <v>74.4884041176837</v>
+        <v>74.48840411768369</v>
       </c>
     </row>
     <row r="1058">
@@ -14127,7 +14127,7 @@
         <v>2026</v>
       </c>
       <c r="D1059">
-        <v>71.5653730903588</v>
+        <v>67.64829124718366</v>
       </c>
     </row>
     <row r="1060">
@@ -14140,7 +14140,7 @@
         <v>2027</v>
       </c>
       <c r="D1060">
-        <v>68.34887165447718</v>
+        <v>64.83889981003881</v>
       </c>
     </row>
     <row r="1061">
@@ -14153,7 +14153,7 @@
         <v>2028</v>
       </c>
       <c r="D1061">
-        <v>64.34514949138561</v>
+        <v>60.54825741693435</v>
       </c>
     </row>
     <row r="1062">
@@ -14166,7 +14166,7 @@
         <v>2024</v>
       </c>
       <c r="D1062">
-        <v>62.73992311652212</v>
+        <v>62.73992311652211</v>
       </c>
     </row>
     <row r="1063">
@@ -14192,7 +14192,7 @@
         <v>2026</v>
       </c>
       <c r="D1064">
-        <v>60.30089716027378</v>
+        <v>57.93822817737999</v>
       </c>
     </row>
     <row r="1065">
@@ -14205,7 +14205,7 @@
         <v>2027</v>
       </c>
       <c r="D1065">
-        <v>57.88276443636806</v>
+        <v>55.48552494480495</v>
       </c>
     </row>
     <row r="1066">
@@ -14218,7 +14218,7 @@
         <v>2028</v>
       </c>
       <c r="D1066">
-        <v>55.52581237936257</v>
+        <v>53.15368401590275</v>
       </c>
     </row>
     <row r="1067">
@@ -14231,7 +14231,7 @@
         <v>2024</v>
       </c>
       <c r="D1067">
-        <v>67.3045850400085</v>
+        <v>67.30458504000849</v>
       </c>
     </row>
     <row r="1068">
@@ -14257,7 +14257,7 @@
         <v>2026</v>
       </c>
       <c r="D1069">
-        <v>63.00935195622268</v>
+        <v>57.45675328484724</v>
       </c>
     </row>
     <row r="1070">
@@ -14270,7 +14270,7 @@
         <v>2027</v>
       </c>
       <c r="D1070">
-        <v>58.66261261750504</v>
+        <v>54.26436702385558</v>
       </c>
     </row>
     <row r="1071">
@@ -14283,7 +14283,7 @@
         <v>2028</v>
       </c>
       <c r="D1071">
-        <v>53.10790406311443</v>
+        <v>47.60259188064049</v>
       </c>
     </row>
     <row r="1072">
@@ -14322,7 +14322,7 @@
         <v>2026</v>
       </c>
       <c r="D1074">
-        <v>32.15943759216726</v>
+        <v>27.34255317808623</v>
       </c>
     </row>
     <row r="1075">
@@ -14335,7 +14335,7 @@
         <v>2027</v>
       </c>
       <c r="D1075">
-        <v>28.8196108686803</v>
+        <v>25.42667687838786</v>
       </c>
     </row>
     <row r="1076">
@@ -14348,7 +14348,7 @@
         <v>2028</v>
       </c>
       <c r="D1076">
-        <v>24.0008832665339</v>
+        <v>19.23341974312761</v>
       </c>
     </row>
     <row r="1077">
@@ -14361,7 +14361,7 @@
         <v>2024</v>
       </c>
       <c r="D1077">
-        <v>60.80528209358563</v>
+        <v>60.80528209358562</v>
       </c>
     </row>
     <row r="1078">
@@ -14387,7 +14387,7 @@
         <v>2026</v>
       </c>
       <c r="D1079">
-        <v>55.5153572870647</v>
+        <v>53.95521909072465</v>
       </c>
     </row>
     <row r="1080">
@@ -14400,7 +14400,7 @@
         <v>2027</v>
       </c>
       <c r="D1080">
-        <v>50.85037895106016</v>
+        <v>46.81034708557203</v>
       </c>
     </row>
     <row r="1081">
@@ -14413,7 +14413,7 @@
         <v>2028</v>
       </c>
       <c r="D1081">
-        <v>49.39495400827324</v>
+        <v>47.41929584852306</v>
       </c>
     </row>
     <row r="1082">
@@ -14452,7 +14452,7 @@
         <v>2026</v>
       </c>
       <c r="D1084">
-        <v>67.23852382961483</v>
+        <v>66.09724586033639</v>
       </c>
     </row>
     <row r="1085">
@@ -14465,7 +14465,7 @@
         <v>2027</v>
       </c>
       <c r="D1085">
-        <v>66.09737870063712</v>
+        <v>64.95823370448271</v>
       </c>
     </row>
     <row r="1086">
@@ -14478,7 +14478,7 @@
         <v>2028</v>
       </c>
       <c r="D1086">
-        <v>64.95824315482072</v>
+        <v>63.81924989964305</v>
       </c>
     </row>
     <row r="1087">
@@ -14517,7 +14517,7 @@
         <v>2026</v>
       </c>
       <c r="D1089">
-        <v>49.60731264422666</v>
+        <v>47.68028080252705</v>
       </c>
     </row>
     <row r="1090">
@@ -14530,7 +14530,7 @@
         <v>2027</v>
       </c>
       <c r="D1090">
-        <v>47.70443294259354</v>
+        <v>45.86450640187965</v>
       </c>
     </row>
     <row r="1091">
@@ -14543,7 +14543,7 @@
         <v>2028</v>
       </c>
       <c r="D1091">
-        <v>45.87954017823326</v>
+        <v>44.09383333029307</v>
       </c>
     </row>
     <row r="1092">
@@ -14582,7 +14582,7 @@
         <v>2026</v>
       </c>
       <c r="D1094">
-        <v>75.83547068276029</v>
+        <v>77.44507294361041</v>
       </c>
     </row>
     <row r="1095">
@@ -14595,7 +14595,7 @@
         <v>2027</v>
       </c>
       <c r="D1095">
-        <v>76.88802957487432</v>
+        <v>78.14131139539037</v>
       </c>
     </row>
     <row r="1096">
@@ -14608,7 +14608,7 @@
         <v>2028</v>
       </c>
       <c r="D1096">
-        <v>78.55080085912711</v>
+        <v>80.06601823838054</v>
       </c>
     </row>
     <row r="1097">
@@ -14621,7 +14621,7 @@
         <v>2024</v>
       </c>
       <c r="D1097">
-        <v>63.52974154675678</v>
+        <v>63.52974154675677</v>
       </c>
     </row>
     <row r="1098">
@@ -14647,7 +14647,7 @@
         <v>2026</v>
       </c>
       <c r="D1099">
-        <v>62.2878037069846</v>
+        <v>61.04627405669083</v>
       </c>
     </row>
     <row r="1100">
@@ -14660,7 +14660,7 @@
         <v>2027</v>
       </c>
       <c r="D1100">
-        <v>61.04626760994103</v>
+        <v>59.80513325562605</v>
       </c>
     </row>
     <row r="1101">
@@ -14673,7 +14673,7 @@
         <v>2028</v>
       </c>
       <c r="D1101">
-        <v>59.80513335744294</v>
+        <v>58.56399276001196</v>
       </c>
     </row>
     <row r="1102">
@@ -14712,7 +14712,7 @@
         <v>2026</v>
       </c>
       <c r="D1104">
-        <v>71.10076987197921</v>
+        <v>70.22722721815784</v>
       </c>
     </row>
     <row r="1105">
@@ -14725,7 +14725,7 @@
         <v>2027</v>
       </c>
       <c r="D1105">
-        <v>70.31669505268071</v>
+        <v>69.85334522802565</v>
       </c>
     </row>
     <row r="1106">
@@ -14738,7 +14738,7 @@
         <v>2028</v>
       </c>
       <c r="D1106">
-        <v>69.88795818189068</v>
+        <v>69.58330209948858</v>
       </c>
     </row>
     <row r="1107">
@@ -14751,7 +14751,7 @@
         <v>2024</v>
       </c>
       <c r="D1107">
-        <v>82.30583363317811</v>
+        <v>82.3058336331781</v>
       </c>
     </row>
     <row r="1108">
@@ -14777,7 +14777,7 @@
         <v>2026</v>
       </c>
       <c r="D1109">
-        <v>80.53450547899531</v>
+        <v>78.80738387640059</v>
       </c>
     </row>
     <row r="1110">
@@ -14790,7 +14790,7 @@
         <v>2027</v>
       </c>
       <c r="D1110">
-        <v>78.78633860129457</v>
+        <v>77.06133300007588</v>
       </c>
     </row>
     <row r="1111">
@@ -14803,7 +14803,7 @@
         <v>2028</v>
       </c>
       <c r="D1111">
-        <v>77.07135195854194</v>
+        <v>75.34533899914932</v>
       </c>
     </row>
     <row r="1112">
@@ -14816,7 +14816,7 @@
         <v>2024</v>
       </c>
       <c r="D1112">
-        <v>87.13322001294166</v>
+        <v>87.13322001294163</v>
       </c>
     </row>
     <row r="1113">
@@ -14842,7 +14842,7 @@
         <v>2026</v>
       </c>
       <c r="D1114">
-        <v>85.68438961350269</v>
+        <v>84.28486883212409</v>
       </c>
     </row>
     <row r="1115">
@@ -14855,7 +14855,7 @@
         <v>2027</v>
       </c>
       <c r="D1115">
-        <v>84.31094520751617</v>
+        <v>83.01288679498211</v>
       </c>
     </row>
     <row r="1116">
@@ -14868,7 +14868,7 @@
         <v>2028</v>
       </c>
       <c r="D1116">
-        <v>83.02667674875455</v>
+        <v>81.78227461915743</v>
       </c>
     </row>
     <row r="1117">
@@ -14881,7 +14881,7 @@
         <v>2024</v>
       </c>
       <c r="D1117">
-        <v>72.98937831271694</v>
+        <v>72.98937831271692</v>
       </c>
     </row>
     <row r="1118">
@@ -14907,7 +14907,7 @@
         <v>2026</v>
       </c>
       <c r="D1119">
-        <v>70.70869892449691</v>
+        <v>68.75832577450896</v>
       </c>
     </row>
     <row r="1120">
@@ -14920,7 +14920,7 @@
         <v>2027</v>
       </c>
       <c r="D1120">
-        <v>68.63876689796719</v>
+        <v>66.77958223312775</v>
       </c>
     </row>
     <row r="1121">
@@ -14933,7 +14933,7 @@
         <v>2028</v>
       </c>
       <c r="D1121">
-        <v>66.82285820949575</v>
+        <v>64.93066662085053</v>
       </c>
     </row>
     <row r="1122">
@@ -14972,7 +14972,7 @@
         <v>2026</v>
       </c>
       <c r="D1124">
-        <v>52.69302493160737</v>
+        <v>50.2533975115706</v>
       </c>
     </row>
     <row r="1125">
@@ -14985,7 +14985,7 @@
         <v>2027</v>
       </c>
       <c r="D1125">
-        <v>50.32579001505682</v>
+        <v>47.88514093195288</v>
       </c>
     </row>
     <row r="1126">
@@ -14998,7 +14998,7 @@
         <v>2028</v>
       </c>
       <c r="D1126">
-        <v>47.84919830628578</v>
+        <v>45.40905647533383</v>
       </c>
     </row>
     <row r="1127">
@@ -15037,7 +15037,7 @@
         <v>2026</v>
       </c>
       <c r="D1129">
-        <v>41.82496993684344</v>
+        <v>39.74919445533568</v>
       </c>
     </row>
     <row r="1130">
@@ -15050,7 +15050,7 @@
         <v>2027</v>
       </c>
       <c r="D1130">
-        <v>39.74919355900158</v>
+        <v>37.67337056560348</v>
       </c>
     </row>
     <row r="1131">
@@ -15063,7 +15063,7 @@
         <v>2028</v>
       </c>
       <c r="D1131">
-        <v>37.67337054803068</v>
+        <v>35.59754662315287</v>
       </c>
     </row>
     <row r="1132">
@@ -15076,7 +15076,7 @@
         <v>2024</v>
       </c>
       <c r="D1132">
-        <v>51.91698768778391</v>
+        <v>51.91698768778392</v>
       </c>
     </row>
     <row r="1133">
@@ -15102,7 +15102,7 @@
         <v>2026</v>
       </c>
       <c r="D1134">
-        <v>49.88416948503687</v>
+        <v>47.92291494617454</v>
       </c>
     </row>
     <row r="1135">
@@ -15115,7 +15115,7 @@
         <v>2027</v>
       </c>
       <c r="D1135">
-        <v>47.948831432186</v>
+        <v>46.1109735292313</v>
       </c>
     </row>
     <row r="1136">
@@ -15128,7 +15128,7 @@
         <v>2028</v>
       </c>
       <c r="D1136">
-        <v>46.12035907785644</v>
+        <v>44.32718875816349</v>
       </c>
     </row>
     <row r="1137">
@@ -15141,7 +15141,7 @@
         <v>2024</v>
       </c>
       <c r="D1137">
-        <v>77.47143593443873</v>
+        <v>77.4714359344387</v>
       </c>
     </row>
     <row r="1138">
@@ -15167,7 +15167,7 @@
         <v>2026</v>
       </c>
       <c r="D1139">
-        <v>75.46627343074113</v>
+        <v>73.46292716902698</v>
       </c>
     </row>
     <row r="1140">
@@ -15180,7 +15180,7 @@
         <v>2027</v>
       </c>
       <c r="D1140">
-        <v>73.46315199805889</v>
+        <v>71.46207163639204</v>
       </c>
     </row>
     <row r="1141">
@@ -15193,7 +15193,7 @@
         <v>2028</v>
       </c>
       <c r="D1141">
-        <v>71.46209946753682</v>
+        <v>69.46129959719141</v>
       </c>
     </row>
     <row r="1142">
@@ -15206,7 +15206,7 @@
         <v>2024</v>
       </c>
       <c r="D1142">
-        <v>64.08841506070817</v>
+        <v>64.08841506070819</v>
       </c>
     </row>
     <row r="1143">
@@ -15232,7 +15232,7 @@
         <v>2026</v>
       </c>
       <c r="D1144">
-        <v>61.21372297263511</v>
+        <v>58.35299419596772</v>
       </c>
     </row>
     <row r="1145">
@@ -15245,7 +15245,7 @@
         <v>2027</v>
       </c>
       <c r="D1145">
-        <v>58.35155456275329</v>
+        <v>55.5019098310627</v>
       </c>
     </row>
     <row r="1146">
@@ -15258,7 +15258,7 @@
         <v>2028</v>
       </c>
       <c r="D1146">
-        <v>55.50205825887699</v>
+        <v>52.65127074960057</v>
       </c>
     </row>
     <row r="1147">
@@ -15271,7 +15271,7 @@
         <v>2024</v>
       </c>
       <c r="D1147">
-        <v>76.33996538220543</v>
+        <v>76.33996538220539</v>
       </c>
     </row>
     <row r="1148">
@@ -15297,7 +15297,7 @@
         <v>2026</v>
       </c>
       <c r="D1149">
-        <v>74.50144601937754</v>
+        <v>72.65786856091128</v>
       </c>
     </row>
     <row r="1150">
@@ -15310,7 +15310,7 @@
         <v>2027</v>
       </c>
       <c r="D1150">
-        <v>72.65893180753982</v>
+        <v>70.81242274669225</v>
       </c>
     </row>
     <row r="1151">
@@ -15323,7 +15323,7 @@
         <v>2028</v>
       </c>
       <c r="D1151">
-        <v>70.81219924490938</v>
+        <v>68.96630642712461</v>
       </c>
     </row>
     <row r="1152">
@@ -15336,7 +15336,7 @@
         <v>2024</v>
       </c>
       <c r="D1152">
-        <v>46.2389934339576</v>
+        <v>46.23899343395759</v>
       </c>
     </row>
     <row r="1153">
@@ -15362,7 +15362,7 @@
         <v>2026</v>
       </c>
       <c r="D1154">
-        <v>45.05707474128562</v>
+        <v>44.03819379697768</v>
       </c>
     </row>
     <row r="1155">
@@ -15375,7 +15375,7 @@
         <v>2027</v>
       </c>
       <c r="D1155">
-        <v>43.91799871604834</v>
+        <v>42.82176535824578</v>
       </c>
     </row>
     <row r="1156">
@@ -15388,7 +15388,7 @@
         <v>2028</v>
       </c>
       <c r="D1156">
-        <v>42.91037586485896</v>
+        <v>41.87116843935341</v>
       </c>
     </row>
     <row r="1157">
@@ -15427,7 +15427,7 @@
         <v>2026</v>
       </c>
       <c r="D1159">
-        <v>87.96553410486507</v>
+        <v>87.68497600252671</v>
       </c>
     </row>
     <row r="1160">
@@ -15440,7 +15440,7 @@
         <v>2027</v>
       </c>
       <c r="D1160">
-        <v>87.71842726102268</v>
+        <v>87.58954141421201</v>
       </c>
     </row>
     <row r="1161">
@@ -15453,7 +15453,7 @@
         <v>2028</v>
       </c>
       <c r="D1161">
-        <v>87.602741722651</v>
+        <v>87.53370775121437</v>
       </c>
     </row>
     <row r="1162">
@@ -15466,7 +15466,7 @@
         <v>2024</v>
       </c>
       <c r="D1162">
-        <v>55.31490564367905</v>
+        <v>55.31490564367903</v>
       </c>
     </row>
     <row r="1163">
@@ -15492,7 +15492,7 @@
         <v>2026</v>
       </c>
       <c r="D1164">
-        <v>55.93016147932869</v>
+        <v>56.54703602064885</v>
       </c>
     </row>
     <row r="1165">
@@ -15505,7 +15505,7 @@
         <v>2027</v>
       </c>
       <c r="D1165">
-        <v>56.54697089241112</v>
+        <v>57.16533388292635</v>
       </c>
     </row>
     <row r="1166">
@@ -15518,7 +15518,7 @@
         <v>2028</v>
       </c>
       <c r="D1166">
-        <v>57.16533650334551</v>
+        <v>57.78363960646134</v>
       </c>
     </row>
     <row r="1167">
@@ -15557,7 +15557,7 @@
         <v>2026</v>
       </c>
       <c r="D1169">
-        <v>36.69460969580096</v>
+        <v>33.75813172572271</v>
       </c>
     </row>
     <row r="1170">
@@ -15570,7 +15570,7 @@
         <v>2027</v>
       </c>
       <c r="D1170">
-        <v>33.75752377886242</v>
+        <v>30.82996356131054</v>
       </c>
     </row>
     <row r="1171">
@@ -15583,7 +15583,7 @@
         <v>2028</v>
       </c>
       <c r="D1171">
-        <v>30.83000003380779</v>
+        <v>27.90190481439013</v>
       </c>
     </row>
     <row r="1172">
@@ -15622,7 +15622,7 @@
         <v>2026</v>
       </c>
       <c r="D1174">
-        <v>64.81138226870299</v>
+        <v>62.35940268482005</v>
       </c>
     </row>
     <row r="1175">
@@ -15635,7 +15635,7 @@
         <v>2027</v>
       </c>
       <c r="D1175">
-        <v>60.77987617561175</v>
+        <v>57.14563066166658</v>
       </c>
     </row>
     <row r="1176">
@@ -15648,7 +15648,7 @@
         <v>2028</v>
       </c>
       <c r="D1176">
-        <v>58.40773117213112</v>
+        <v>55.71816016990673</v>
       </c>
     </row>
     <row r="1177">
@@ -15661,7 +15661,7 @@
         <v>2024</v>
       </c>
       <c r="D1177">
-        <v>54.82919308428439</v>
+        <v>54.82919308428436</v>
       </c>
     </row>
     <row r="1178">
@@ -15687,7 +15687,7 @@
         <v>2026</v>
       </c>
       <c r="D1179">
-        <v>51.78722716742156</v>
+        <v>48.74298541381501</v>
       </c>
     </row>
     <row r="1180">
@@ -15700,7 +15700,7 @@
         <v>2027</v>
       </c>
       <c r="D1180">
-        <v>48.74315114459068</v>
+        <v>45.69696501579178</v>
       </c>
     </row>
     <row r="1181">
@@ -15713,7 +15713,7 @@
         <v>2028</v>
       </c>
       <c r="D1181">
-        <v>45.69695294696035</v>
+        <v>42.65090841127428</v>
       </c>
     </row>
     <row r="1182">
@@ -15726,7 +15726,7 @@
         <v>2024</v>
       </c>
       <c r="D1182">
-        <v>63.47201531725342</v>
+        <v>63.47201531725339</v>
       </c>
     </row>
     <row r="1183">
@@ -15752,7 +15752,7 @@
         <v>2026</v>
       </c>
       <c r="D1184">
-        <v>60.48394143329134</v>
+        <v>57.49218805058282</v>
       </c>
     </row>
     <row r="1185">
@@ -15765,7 +15765,7 @@
         <v>2027</v>
       </c>
       <c r="D1185">
-        <v>57.493554641848</v>
+        <v>54.5008549429234</v>
       </c>
     </row>
     <row r="1186">
@@ -15778,7 +15778,7 @@
         <v>2028</v>
       </c>
       <c r="D1186">
-        <v>54.50034738148236</v>
+        <v>51.50799915094084</v>
       </c>
     </row>
     <row r="1187">
@@ -15817,7 +15817,7 @@
         <v>2026</v>
       </c>
       <c r="D1189">
-        <v>35.15235848742753</v>
+        <v>32.34585373190207</v>
       </c>
     </row>
     <row r="1190">
@@ -15830,7 +15830,7 @@
         <v>2027</v>
       </c>
       <c r="D1190">
-        <v>32.39008497655269</v>
+        <v>29.53015704518005</v>
       </c>
     </row>
     <row r="1191">
@@ -15843,7 +15843,7 @@
         <v>2028</v>
       </c>
       <c r="D1191">
-        <v>29.5163684570144</v>
+        <v>26.67309459396106</v>
       </c>
     </row>
     <row r="1192">
@@ -15882,7 +15882,7 @@
         <v>2026</v>
       </c>
       <c r="D1194">
-        <v>59.00234894790475</v>
+        <v>57.93888914747936</v>
       </c>
     </row>
     <row r="1195">
@@ -15895,7 +15895,7 @@
         <v>2027</v>
       </c>
       <c r="D1195">
-        <v>58.0663642855688</v>
+        <v>56.86630728808183</v>
       </c>
     </row>
     <row r="1196">
@@ -15908,7 +15908,7 @@
         <v>2028</v>
       </c>
       <c r="D1196">
-        <v>56.82480552407748</v>
+        <v>55.6692201366713</v>
       </c>
     </row>
     <row r="1197">
@@ -15921,7 +15921,7 @@
         <v>2024</v>
       </c>
       <c r="D1197">
-        <v>53.852256207643</v>
+        <v>53.85225620764301</v>
       </c>
     </row>
     <row r="1198">
@@ -15947,7 +15947,7 @@
         <v>2026</v>
       </c>
       <c r="D1199">
-        <v>52.68271214804477</v>
+        <v>51.65973011610393</v>
       </c>
     </row>
     <row r="1200">
@@ -15960,7 +15960,7 @@
         <v>2027</v>
       </c>
       <c r="D1200">
-        <v>51.61671577789204</v>
+        <v>50.65426709718481</v>
       </c>
     </row>
     <row r="1201">
@@ -15973,7 +15973,7 @@
         <v>2028</v>
       </c>
       <c r="D1201">
-        <v>50.66689133090606</v>
+        <v>49.68667677942945</v>
       </c>
     </row>
     <row r="1202">
@@ -15986,7 +15986,7 @@
         <v>2024</v>
       </c>
       <c r="D1202">
-        <v>52.15682075637249</v>
+        <v>52.15682075637248</v>
       </c>
     </row>
     <row r="1203">
@@ -16012,7 +16012,7 @@
         <v>2026</v>
       </c>
       <c r="D1204">
-        <v>48.6276455130768</v>
+        <v>45.04203775570471</v>
       </c>
     </row>
     <row r="1205">
@@ -16025,7 +16025,7 @@
         <v>2027</v>
       </c>
       <c r="D1205">
-        <v>45.05124291016188</v>
+        <v>41.42761294762774</v>
       </c>
     </row>
     <row r="1206">
@@ -16038,7 +16038,7 @@
         <v>2028</v>
       </c>
       <c r="D1206">
-        <v>41.42611142195647</v>
+        <v>37.80868356253695</v>
       </c>
     </row>
     <row r="1207">
@@ -16051,7 +16051,7 @@
         <v>2024</v>
       </c>
       <c r="D1207">
-        <v>62.83826146806033</v>
+        <v>62.83826146806031</v>
       </c>
     </row>
     <row r="1208">
@@ -16077,7 +16077,7 @@
         <v>2026</v>
       </c>
       <c r="D1209">
-        <v>61.37769496575035</v>
+        <v>62.81741316466206</v>
       </c>
     </row>
     <row r="1210">
@@ -16090,7 +16090,7 @@
         <v>2027</v>
       </c>
       <c r="D1210">
-        <v>60.07080164906125</v>
+        <v>58.91758151799302</v>
       </c>
     </row>
     <row r="1211">
@@ -16103,7 +16103,7 @@
         <v>2028</v>
       </c>
       <c r="D1211">
-        <v>61.51866230652846</v>
+        <v>62.82099223693034</v>
       </c>
     </row>
     <row r="1212">
@@ -16116,7 +16116,7 @@
         <v>2024</v>
       </c>
       <c r="D1212">
-        <v>74.89105760790335</v>
+        <v>74.89105760790332</v>
       </c>
     </row>
     <row r="1213">
@@ -16142,7 +16142,7 @@
         <v>2026</v>
       </c>
       <c r="D1214">
-        <v>73.66308095709043</v>
+        <v>72.43574739399102</v>
       </c>
     </row>
     <row r="1215">
@@ -16155,7 +16155,7 @@
         <v>2027</v>
       </c>
       <c r="D1215">
-        <v>72.4354992004982</v>
+        <v>71.20831233812666</v>
       </c>
     </row>
     <row r="1216">
@@ -16168,7 +16168,7 @@
         <v>2028</v>
       </c>
       <c r="D1216">
-        <v>71.20840812600845</v>
+        <v>69.98116464590763</v>
       </c>
     </row>
     <row r="1217">
@@ -16181,7 +16181,7 @@
         <v>2024</v>
       </c>
       <c r="D1217">
-        <v>82.55298760168711</v>
+        <v>82.55298760168712</v>
       </c>
     </row>
     <row r="1218">
@@ -16207,7 +16207,7 @@
         <v>2026</v>
       </c>
       <c r="D1219">
-        <v>88.04139631203854</v>
+        <v>92.9401191893721</v>
       </c>
     </row>
     <row r="1220">
@@ -16220,7 +16220,7 @@
         <v>2027</v>
       </c>
       <c r="D1220">
-        <v>92.55488826967303</v>
+        <v>96.09346347459058</v>
       </c>
     </row>
     <row r="1221">
@@ -16233,7 +16233,7 @@
         <v>2028</v>
       </c>
       <c r="D1221">
-        <v>95.84179919306511</v>
+        <v>98.49181491523261</v>
       </c>
     </row>
     <row r="1222">
@@ -16272,7 +16272,7 @@
         <v>2026</v>
       </c>
       <c r="D1224">
-        <v>93.23086577866825</v>
+        <v>94.52181712605636</v>
       </c>
     </row>
     <row r="1225">
@@ -16285,7 +16285,7 @@
         <v>2027</v>
       </c>
       <c r="D1225">
-        <v>94.51048311825207</v>
+        <v>95.81523424624797</v>
       </c>
     </row>
     <row r="1226">
@@ -16298,7 +16298,7 @@
         <v>2028</v>
       </c>
       <c r="D1226">
-        <v>95.81875679891732</v>
+        <v>97.11921902444769</v>
       </c>
     </row>
     <row r="1227">
@@ -16337,7 +16337,7 @@
         <v>2026</v>
       </c>
       <c r="D1229">
-        <v>62.78135675046257</v>
+        <v>61.4619202289159</v>
       </c>
     </row>
     <row r="1230">
@@ -16350,7 +16350,7 @@
         <v>2027</v>
       </c>
       <c r="D1230">
-        <v>60.44506045214862</v>
+        <v>58.19016958681383</v>
       </c>
     </row>
     <row r="1231">
@@ -16363,7 +16363,7 @@
         <v>2028</v>
       </c>
       <c r="D1231">
-        <v>59.13165785069676</v>
+        <v>57.74288373636057</v>
       </c>
     </row>
     <row r="1232">
@@ -16402,7 +16402,7 @@
         <v>2026</v>
       </c>
       <c r="D1234">
-        <v>70.5149649755091</v>
+        <v>68.81233629999667</v>
       </c>
     </row>
     <row r="1235">
@@ -16415,7 +16415,7 @@
         <v>2027</v>
       </c>
       <c r="D1235">
-        <v>69.14493761448223</v>
+        <v>67.65486153929734</v>
       </c>
     </row>
     <row r="1236">
@@ -16428,7 +16428,7 @@
         <v>2028</v>
       </c>
       <c r="D1236">
-        <v>67.41047044817331</v>
+        <v>65.76421350522595</v>
       </c>
     </row>
     <row r="1237">
@@ -16441,7 +16441,7 @@
         <v>2024</v>
       </c>
       <c r="D1237">
-        <v>78.337793371225</v>
+        <v>78.33779337122502</v>
       </c>
     </row>
     <row r="1238">
@@ -16467,7 +16467,7 @@
         <v>2026</v>
       </c>
       <c r="D1239">
-        <v>76.83809295598724</v>
+        <v>75.34012586293862</v>
       </c>
     </row>
     <row r="1240">
@@ -16480,7 +16480,7 @@
         <v>2027</v>
       </c>
       <c r="D1240">
-        <v>75.34020063115288</v>
+        <v>73.84411639672197</v>
       </c>
     </row>
     <row r="1241">
@@ -16493,7 +16493,7 @@
         <v>2028</v>
       </c>
       <c r="D1241">
-        <v>73.84411962190762</v>
+        <v>72.34811660606231</v>
       </c>
     </row>
     <row r="1242">
@@ -16506,7 +16506,7 @@
         <v>2024</v>
       </c>
       <c r="D1242">
-        <v>94.54365850661613</v>
+        <v>94.54365850661611</v>
       </c>
     </row>
     <row r="1243">
@@ -16532,7 +16532,7 @@
         <v>2026</v>
       </c>
       <c r="D1244">
-        <v>93.49311716380481</v>
+        <v>95.83554573130849</v>
       </c>
     </row>
     <row r="1245">
@@ -16545,7 +16545,7 @@
         <v>2027</v>
       </c>
       <c r="D1245">
-        <v>92.81036625192199</v>
+        <v>92.49540577096764</v>
       </c>
     </row>
     <row r="1246">
@@ -16558,7 +16558,7 @@
         <v>2028</v>
       </c>
       <c r="D1246">
-        <v>95.19266248835821</v>
+        <v>97.24703596279849</v>
       </c>
     </row>
     <row r="1247">
@@ -16571,7 +16571,7 @@
         <v>2024</v>
       </c>
       <c r="D1247">
-        <v>85.49610022989958</v>
+        <v>85.4961002298996</v>
       </c>
     </row>
     <row r="1248">
@@ -16597,7 +16597,7 @@
         <v>2026</v>
       </c>
       <c r="D1249">
-        <v>85.21637623631297</v>
+        <v>84.93665224272635</v>
       </c>
     </row>
     <row r="1250">
@@ -16610,7 +16610,7 @@
         <v>2027</v>
       </c>
       <c r="D1250">
-        <v>84.93665224272637</v>
+        <v>84.65692824913975</v>
       </c>
     </row>
     <row r="1251">
@@ -16623,7 +16623,7 @@
         <v>2028</v>
       </c>
       <c r="D1251">
-        <v>84.65692824913975</v>
+        <v>84.37720425555317</v>
       </c>
     </row>
     <row r="1252">
@@ -16636,7 +16636,7 @@
         <v>2024</v>
       </c>
       <c r="D1252">
-        <v>87.69016777274572</v>
+        <v>87.69016777274571</v>
       </c>
     </row>
     <row r="1253">
@@ -16662,7 +16662,7 @@
         <v>2026</v>
       </c>
       <c r="D1254">
-        <v>88.34995865500578</v>
+        <v>88.55595473318188</v>
       </c>
     </row>
     <row r="1255">
@@ -16675,7 +16675,7 @@
         <v>2027</v>
       </c>
       <c r="D1255">
-        <v>88.9752163792367</v>
+        <v>89.56594094543846</v>
       </c>
     </row>
     <row r="1256">
@@ -16688,7 +16688,7 @@
         <v>2028</v>
       </c>
       <c r="D1256">
-        <v>89.17858453176724</v>
+        <v>89.41385791668141</v>
       </c>
     </row>
     <row r="1257">
@@ -16701,7 +16701,7 @@
         <v>2024</v>
       </c>
       <c r="D1257">
-        <v>56.14661052316922</v>
+        <v>56.1466105231692</v>
       </c>
     </row>
     <row r="1258">
@@ -16727,7 +16727,7 @@
         <v>2026</v>
       </c>
       <c r="D1259">
-        <v>53.86391498564342</v>
+        <v>51.62538328758083</v>
       </c>
     </row>
     <row r="1260">
@@ -16740,7 +16740,7 @@
         <v>2027</v>
       </c>
       <c r="D1260">
-        <v>51.61323002259902</v>
+        <v>49.39455563403602</v>
       </c>
     </row>
     <row r="1261">
@@ -16753,7 +16753,7 @@
         <v>2028</v>
       </c>
       <c r="D1261">
-        <v>49.39790004094252</v>
+        <v>47.17376120121071</v>
       </c>
     </row>
     <row r="1262">
@@ -16766,7 +16766,7 @@
         <v>2024</v>
       </c>
       <c r="D1262">
-        <v>62.26548297938494</v>
+        <v>62.26548297938495</v>
       </c>
     </row>
     <row r="1263">
@@ -16792,7 +16792,7 @@
         <v>2026</v>
       </c>
       <c r="D1264">
-        <v>58.5707467362387</v>
+        <v>54.87495412752362</v>
       </c>
     </row>
     <row r="1265">
@@ -16805,7 +16805,7 @@
         <v>2027</v>
       </c>
       <c r="D1265">
-        <v>54.87499750965033</v>
+        <v>51.17823529961986</v>
       </c>
     </row>
     <row r="1266">
@@ -16818,7 +16818,7 @@
         <v>2028</v>
       </c>
       <c r="D1266">
-        <v>51.1782335180312</v>
+        <v>47.48151112695012</v>
       </c>
     </row>
     <row r="1267">
@@ -16831,7 +16831,7 @@
         <v>2024</v>
       </c>
       <c r="D1267">
-        <v>82.02018677058368</v>
+        <v>82.02018677058366</v>
       </c>
     </row>
     <row r="1268">
@@ -16857,7 +16857,7 @@
         <v>2026</v>
       </c>
       <c r="D1269">
-        <v>79.65769791605096</v>
+        <v>77.29541464915448</v>
       </c>
     </row>
     <row r="1270">
@@ -16870,7 +16870,7 @@
         <v>2027</v>
       </c>
       <c r="D1270">
-        <v>77.29541189687534</v>
+        <v>74.93332871305678</v>
       </c>
     </row>
     <row r="1271">
@@ -16883,7 +16883,7 @@
         <v>2028</v>
       </c>
       <c r="D1271">
-        <v>74.93332874990257</v>
+        <v>72.5712428874965</v>
       </c>
     </row>
     <row r="1272">
@@ -16922,7 +16922,7 @@
         <v>2026</v>
       </c>
       <c r="D1274">
-        <v>69.92004637282893</v>
+        <v>65.68549185557892</v>
       </c>
     </row>
     <row r="1275">
@@ -16935,7 +16935,7 @@
         <v>2027</v>
       </c>
       <c r="D1275">
-        <v>68.2517765295312</v>
+        <v>66.42942530826568</v>
       </c>
     </row>
     <row r="1276">
@@ -16948,7 +16948,7 @@
         <v>2028</v>
       </c>
       <c r="D1276">
-        <v>64.00849485182435</v>
+        <v>59.91056739162848</v>
       </c>
     </row>
     <row r="1277">
@@ -16961,7 +16961,7 @@
         <v>2024</v>
       </c>
       <c r="D1277">
-        <v>85.18791766163881</v>
+        <v>85.18791766163879</v>
       </c>
     </row>
     <row r="1278">
@@ -16987,7 +16987,7 @@
         <v>2026</v>
       </c>
       <c r="D1279">
-        <v>82.33890812962439</v>
+        <v>78.42032536194935</v>
       </c>
     </row>
     <row r="1280">
@@ -17000,7 +17000,7 @@
         <v>2027</v>
       </c>
       <c r="D1280">
-        <v>79.46735899488546</v>
+        <v>76.57327025742202</v>
       </c>
     </row>
     <row r="1281">
@@ -17013,7 +17013,7 @@
         <v>2028</v>
       </c>
       <c r="D1281">
-        <v>75.54830123992201</v>
+        <v>71.65130810039464</v>
       </c>
     </row>
     <row r="1282">
@@ -17026,7 +17026,7 @@
         <v>2024</v>
       </c>
       <c r="D1282">
-        <v>55.51986491180743</v>
+        <v>55.5198649118074</v>
       </c>
     </row>
     <row r="1283">
@@ -17052,7 +17052,7 @@
         <v>2026</v>
       </c>
       <c r="D1284">
-        <v>51.67353066824729</v>
+        <v>45.01989217297913</v>
       </c>
     </row>
     <row r="1285">
@@ -17065,7 +17065,7 @@
         <v>2027</v>
       </c>
       <c r="D1285">
-        <v>47.72768205106424</v>
+        <v>43.68231906025827</v>
       </c>
     </row>
     <row r="1286">
@@ -17078,7 +17078,7 @@
         <v>2028</v>
       </c>
       <c r="D1286">
-        <v>41.07051593297017</v>
+        <v>34.50933656567314</v>
       </c>
     </row>
     <row r="1287">
@@ -17091,7 +17091,7 @@
         <v>2024</v>
       </c>
       <c r="D1287">
-        <v>14.65209861178184</v>
+        <v>14.65209861178183</v>
       </c>
     </row>
     <row r="1288">
@@ -17117,7 +17117,7 @@
         <v>2026</v>
       </c>
       <c r="D1289">
-        <v>15.42396098102499</v>
+        <v>16.19739216498904</v>
       </c>
     </row>
     <row r="1290">
@@ -17130,7 +17130,7 @@
         <v>2027</v>
       </c>
       <c r="D1290">
-        <v>16.19771962941394</v>
+        <v>16.97337455694868</v>
       </c>
     </row>
     <row r="1291">
@@ -17143,7 +17143,7 @@
         <v>2028</v>
       </c>
       <c r="D1291">
-        <v>16.97344290979376</v>
+        <v>17.74956200744356</v>
       </c>
     </row>
     <row r="1292">
@@ -17156,7 +17156,7 @@
         <v>2024</v>
       </c>
       <c r="D1292">
-        <v>43.29389626405985</v>
+        <v>43.29389626405986</v>
       </c>
     </row>
     <row r="1293">
@@ -17182,7 +17182,7 @@
         <v>2026</v>
       </c>
       <c r="D1294">
-        <v>43.45415674911674</v>
+        <v>43.61410419859973</v>
       </c>
     </row>
     <row r="1295">
@@ -17195,7 +17195,7 @@
         <v>2027</v>
       </c>
       <c r="D1295">
-        <v>43.61401962627622</v>
+        <v>43.77348489553827</v>
       </c>
     </row>
     <row r="1296">
@@ -17208,7 +17208,7 @@
         <v>2028</v>
       </c>
       <c r="D1296">
-        <v>43.77346204676804</v>
+        <v>43.93279704616614</v>
       </c>
     </row>
     <row r="1297">
@@ -17247,7 +17247,7 @@
         <v>2026</v>
       </c>
       <c r="D1299">
-        <v>89.78141271912079</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1300">
@@ -17260,7 +17260,7 @@
         <v>2027</v>
       </c>
       <c r="D1300">
-        <v>99.89735125416378</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1301">
@@ -17286,7 +17286,7 @@
         <v>2024</v>
       </c>
       <c r="D1302">
-        <v>40.33726682913038</v>
+        <v>40.33726682913037</v>
       </c>
     </row>
     <row r="1303">
@@ -17312,7 +17312,7 @@
         <v>2026</v>
       </c>
       <c r="D1304">
-        <v>38.94638522577602</v>
+        <v>37.64253157148518</v>
       </c>
     </row>
     <row r="1305">
@@ -17325,7 +17325,7 @@
         <v>2027</v>
       </c>
       <c r="D1305">
-        <v>37.60665040850532</v>
+        <v>36.31806237731828</v>
       </c>
     </row>
     <row r="1306">
@@ -17338,7 +17338,7 @@
         <v>2028</v>
       </c>
       <c r="D1306">
-        <v>36.33285599098654</v>
+        <v>35.03797402415617</v>
       </c>
     </row>
     <row r="1307">
@@ -17377,7 +17377,7 @@
         <v>2026</v>
       </c>
       <c r="D1309">
-        <v>10.25322301780453</v>
+        <v>7.151448832351107</v>
       </c>
     </row>
     <row r="1310">
@@ -17390,7 +17390,7 @@
         <v>2027</v>
       </c>
       <c r="D1310">
-        <v>7.152970571453587</v>
+        <v>4.069274867765365</v>
       </c>
     </row>
     <row r="1311">
@@ -17403,7 +17403,7 @@
         <v>2028</v>
       </c>
       <c r="D1311">
-        <v>4.069428887675421</v>
+        <v>0.9875629629097915</v>
       </c>
     </row>
     <row r="1312">
@@ -17416,7 +17416,7 @@
         <v>2024</v>
       </c>
       <c r="D1312">
-        <v>56.94392399538179</v>
+        <v>56.94392399538178</v>
       </c>
     </row>
     <row r="1313">
@@ -17442,7 +17442,7 @@
         <v>2026</v>
       </c>
       <c r="D1314">
-        <v>52.99404077707814</v>
+        <v>50.18900933304168</v>
       </c>
     </row>
     <row r="1315">
@@ -17455,7 +17455,7 @@
         <v>2027</v>
       </c>
       <c r="D1315">
-        <v>49.2159278817042</v>
+        <v>45.60958530925996</v>
       </c>
     </row>
     <row r="1316">
@@ -17468,7 +17468,7 @@
         <v>2028</v>
       </c>
       <c r="D1316">
-        <v>46.43666837120757</v>
+        <v>43.51141047132107</v>
       </c>
     </row>
     <row r="1317">
@@ -17481,7 +17481,7 @@
         <v>2024</v>
       </c>
       <c r="D1317">
-        <v>61.32586757009275</v>
+        <v>61.32586757009274</v>
       </c>
     </row>
     <row r="1318">
@@ -17507,7 +17507,7 @@
         <v>2026</v>
       </c>
       <c r="D1319">
-        <v>59.37027421284285</v>
+        <v>56.00320462488555</v>
       </c>
     </row>
     <row r="1320">
@@ -17520,7 +17520,7 @@
         <v>2027</v>
       </c>
       <c r="D1320">
-        <v>57.3458478298059</v>
+        <v>55.2525884209819</v>
       </c>
     </row>
     <row r="1321">
@@ -17533,7 +17533,7 @@
         <v>2028</v>
       </c>
       <c r="D1321">
-        <v>53.97542148292067</v>
+        <v>50.67047140289453</v>
       </c>
     </row>
     <row r="1322">
@@ -17572,7 +17572,7 @@
         <v>2026</v>
       </c>
       <c r="D1324">
-        <v>65.46302987741127</v>
+        <v>66.99735173686688</v>
       </c>
     </row>
     <row r="1325">
@@ -17585,7 +17585,7 @@
         <v>2027</v>
       </c>
       <c r="D1325">
-        <v>66.99734957465186</v>
+        <v>68.53160483354544</v>
       </c>
     </row>
     <row r="1326">
@@ -17598,7 +17598,7 @@
         <v>2028</v>
       </c>
       <c r="D1326">
-        <v>68.53160475847376</v>
+        <v>70.06585770500898</v>
       </c>
     </row>
     <row r="1327">
@@ -17637,7 +17637,7 @@
         <v>2026</v>
       </c>
       <c r="D1329">
-        <v>65.03316150208776</v>
+        <v>64.42296153054346</v>
       </c>
     </row>
     <row r="1330">
@@ -17650,7 +17650,7 @@
         <v>2027</v>
       </c>
       <c r="D1330">
-        <v>64.33837677834769</v>
+        <v>63.65831735328072</v>
       </c>
     </row>
     <row r="1331">
@@ -17663,7 +17663,7 @@
         <v>2028</v>
       </c>
       <c r="D1331">
-        <v>63.73036021542231</v>
+        <v>63.10980176244274</v>
       </c>
     </row>
     <row r="1332">
@@ -17676,7 +17676,7 @@
         <v>2024</v>
       </c>
       <c r="D1332">
-        <v>47.08499713349372</v>
+        <v>47.08499713349371</v>
       </c>
     </row>
     <row r="1333">
@@ -17702,7 +17702,7 @@
         <v>2026</v>
       </c>
       <c r="D1334">
-        <v>44.12716696394225</v>
+        <v>35.85369251349186</v>
       </c>
     </row>
     <row r="1335">
@@ -17715,7 +17715,7 @@
         <v>2027</v>
       </c>
       <c r="D1335">
-        <v>40.86952212842596</v>
+        <v>37.31206262694484</v>
       </c>
     </row>
     <row r="1336">
@@ -17728,7 +17728,7 @@
         <v>2028</v>
       </c>
       <c r="D1336">
-        <v>32.57913743545792</v>
+        <v>24.57165716593705</v>
       </c>
     </row>
     <row r="1337">
@@ -17767,7 +17767,7 @@
         <v>2026</v>
       </c>
       <c r="D1339">
-        <v>77.2793316712356</v>
+        <v>78.56223465915207</v>
       </c>
     </row>
     <row r="1340">
@@ -17780,7 +17780,7 @@
         <v>2027</v>
       </c>
       <c r="D1340">
-        <v>78.56450378584898</v>
+        <v>79.83313094818459</v>
       </c>
     </row>
     <row r="1341">
@@ -17793,7 +17793,7 @@
         <v>2028</v>
       </c>
       <c r="D1341">
-        <v>79.8328572735618</v>
+        <v>81.10320621334873</v>
       </c>
     </row>
   </sheetData>
